--- a/trygt.xlsx
+++ b/trygt.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/amit/BIO/FINAL/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139F4957-F548-1647-87CC-A5860E6B8016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4740" yWindow="2860" windowWidth="24440" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -112,8 +118,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,13 +182,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -220,7 +234,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -254,6 +268,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -288,9 +303,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -463,11 +479,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE231"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="25" max="25" width="22.6640625" customWidth="1"/>
+    <col min="26" max="26" width="27.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,7 +579,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -567,10 +587,10 @@
         <v>12911</v>
       </c>
       <c r="C2">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="D2">
-        <v>19.81</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="E2">
         <v>22.35</v>
@@ -588,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>17.98</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>16.86</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>131.88</v>
@@ -612,10 +632,10 @@
         <v>12911</v>
       </c>
       <c r="R2">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="S2">
-        <v>19.81</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="T2">
         <v>22.35</v>
@@ -654,7 +674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -665,10 +685,10 @@
         <v>9.02</v>
       </c>
       <c r="D3">
-        <v>40.45</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="E3">
-        <v>39.41</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -683,10 +703,10 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>19.02</v>
+        <v>0.01</v>
       </c>
       <c r="K3">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>350.43</v>
@@ -710,10 +730,10 @@
         <v>9.02</v>
       </c>
       <c r="S3">
-        <v>40.45</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="T3">
-        <v>39.41</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -749,7 +769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -763,7 +783,7 @@
         <v>45.32</v>
       </c>
       <c r="E4">
-        <v>75.68000000000001</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -778,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>21.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K4">
-        <v>17.08</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>179.02</v>
@@ -808,7 +828,7 @@
         <v>45.32</v>
       </c>
       <c r="T4">
-        <v>75.68000000000001</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -844,7 +864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -852,7 +872,7 @@
         <v>10999</v>
       </c>
       <c r="C5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D5">
         <v>20.58</v>
@@ -873,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>23.98</v>
+        <v>0.15</v>
       </c>
       <c r="K5">
-        <v>17.96</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>74.11</v>
@@ -897,7 +917,7 @@
         <v>10999</v>
       </c>
       <c r="R5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="S5">
         <v>20.58</v>
@@ -939,7 +959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -968,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>0.17</v>
       </c>
       <c r="K6">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>226.02</v>
@@ -1034,7 +1054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1045,7 +1065,7 @@
         <v>1.7</v>
       </c>
       <c r="D7">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="E7">
         <v>57.21</v>
@@ -1063,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>19.18</v>
+        <v>0.03</v>
       </c>
       <c r="K7">
-        <v>17.59</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>72.31</v>
@@ -1090,7 +1110,7 @@
         <v>1.7</v>
       </c>
       <c r="S7">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="T7">
         <v>57.21</v>
@@ -1129,7 +1149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1152,19 +1172,19 @@
         <v>0.72</v>
       </c>
       <c r="H8">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>17.75</v>
+        <v>0.01</v>
       </c>
       <c r="K8">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>72.04000000000001</v>
+        <v>72.040000000000006</v>
       </c>
       <c r="M8">
         <v>1000.19</v>
@@ -1197,7 +1217,7 @@
         <v>0.72</v>
       </c>
       <c r="W8">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X8">
         <v>0</v>
@@ -1209,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>72.04000000000001</v>
+        <v>72.040000000000006</v>
       </c>
       <c r="AB8">
         <v>1000.19</v>
@@ -1224,7 +1244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1232,7 +1252,7 @@
         <v>35913</v>
       </c>
       <c r="C9">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="D9">
         <v>41.89</v>
@@ -1247,16 +1267,16 @@
         <v>0.93</v>
       </c>
       <c r="H9">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>19.41</v>
+        <v>0.02</v>
       </c>
       <c r="K9">
-        <v>18.55</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>301.14</v>
@@ -1277,7 +1297,7 @@
         <v>35913</v>
       </c>
       <c r="R9">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="S9">
         <v>41.89</v>
@@ -1292,7 +1312,7 @@
         <v>0.93</v>
       </c>
       <c r="W9">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -1319,7 +1339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1333,7 +1353,7 @@
         <v>53.47</v>
       </c>
       <c r="E10">
-        <v>78.90000000000001</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1348,13 +1368,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>22.42</v>
+        <v>0.17</v>
       </c>
       <c r="K10">
-        <v>19.12</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>534.1900000000001</v>
+        <v>534.19000000000005</v>
       </c>
       <c r="M10">
         <v>151.78</v>
@@ -1378,7 +1398,7 @@
         <v>53.47</v>
       </c>
       <c r="T10">
-        <v>78.90000000000001</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1393,13 +1413,13 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>534.1900000000001</v>
+        <v>534.19000000000005</v>
       </c>
       <c r="AB10">
         <v>151.78</v>
@@ -1414,7 +1434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1434,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H11">
         <v>0.06</v>
@@ -1443,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>19.8</v>
+        <v>0.05</v>
       </c>
       <c r="K11">
-        <v>18.52</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>417.31</v>
@@ -1479,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="V11">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W11">
         <v>0.06</v>
@@ -1509,7 +1529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1517,7 +1537,7 @@
         <v>29926</v>
       </c>
       <c r="C12">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D12">
         <v>35.6</v>
@@ -1538,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>17.76</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>17.43</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>265.42</v>
@@ -1562,7 +1582,7 @@
         <v>29926</v>
       </c>
       <c r="R12">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="S12">
         <v>35.6</v>
@@ -1604,7 +1624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1612,7 +1632,7 @@
         <v>7471</v>
       </c>
       <c r="C13">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D13">
         <v>27.16</v>
@@ -1633,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>17.56</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>17.55</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>225.5</v>
@@ -1657,7 +1677,7 @@
         <v>7471</v>
       </c>
       <c r="R13">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="S13">
         <v>27.16</v>
@@ -1699,7 +1719,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1728,10 +1748,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>18.72</v>
+        <v>0.01</v>
       </c>
       <c r="K14">
-        <v>18.09</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>390.97</v>
@@ -1794,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1808,7 +1828,7 @@
         <v>59.8</v>
       </c>
       <c r="E15">
-        <v>81.43000000000001</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1823,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>25.38</v>
+        <v>0.23</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1853,7 +1873,7 @@
         <v>59.8</v>
       </c>
       <c r="T15">
-        <v>81.43000000000001</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -1889,7 +1909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1918,16 +1938,16 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>23.58</v>
+        <v>0.21</v>
       </c>
       <c r="K16">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>565.04</v>
       </c>
       <c r="M16">
-        <v>295.29</v>
+        <v>295.29000000000002</v>
       </c>
       <c r="N16" t="s">
         <v>30</v>
@@ -1972,7 +1992,7 @@
         <v>565.04</v>
       </c>
       <c r="AB16">
-        <v>295.29</v>
+        <v>295.29000000000002</v>
       </c>
       <c r="AC16" t="s">
         <v>30</v>
@@ -1984,7 +2004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1995,7 +2015,7 @@
         <v>1.77</v>
       </c>
       <c r="D17">
-        <v>37.84</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="E17">
         <v>74.36</v>
@@ -2013,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>18.67</v>
+        <v>0.03</v>
       </c>
       <c r="K17">
-        <v>17.59</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>567.21</v>
@@ -2040,7 +2060,7 @@
         <v>1.77</v>
       </c>
       <c r="S17">
-        <v>37.84</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="T17">
         <v>74.36</v>
@@ -2079,7 +2099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2108,16 +2128,16 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>20.22</v>
+        <v>0.05</v>
       </c>
       <c r="K18">
-        <v>18.83</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>1016.96</v>
       </c>
       <c r="M18">
-        <v>574.58</v>
+        <v>574.58000000000004</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -2162,7 +2182,7 @@
         <v>1016.96</v>
       </c>
       <c r="AB18">
-        <v>574.58</v>
+        <v>574.58000000000004</v>
       </c>
       <c r="AC18" t="s">
         <v>30</v>
@@ -2174,7 +2194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2185,7 +2205,7 @@
         <v>5.38</v>
       </c>
       <c r="D19">
-        <v>69.65000000000001</v>
+        <v>69.650000000000006</v>
       </c>
       <c r="E19">
         <v>86.7</v>
@@ -2203,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>22.9</v>
+        <v>0.18</v>
       </c>
       <c r="K19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>695.05</v>
@@ -2230,7 +2250,7 @@
         <v>5.38</v>
       </c>
       <c r="S19">
-        <v>69.65000000000001</v>
+        <v>69.650000000000006</v>
       </c>
       <c r="T19">
         <v>86.7</v>
@@ -2248,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2269,7 +2289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:31">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2298,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>22.94</v>
+        <v>0.11</v>
       </c>
       <c r="K20">
-        <v>18.98</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>907.76</v>
@@ -2364,7 +2384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2393,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>18.94</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>18.51</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>906.37</v>
@@ -2459,7 +2479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2488,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>25.28</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2554,7 +2574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2568,7 +2588,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>38.27</v>
+        <v>38.270000000000003</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2583,16 +2603,16 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>18.66</v>
+        <v>0.01</v>
       </c>
       <c r="K23">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>864.53</v>
       </c>
       <c r="M23">
-        <v>987.9400000000001</v>
+        <v>987.94</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
@@ -2613,7 +2633,7 @@
         <v>29</v>
       </c>
       <c r="T23">
-        <v>38.27</v>
+        <v>38.270000000000003</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2637,7 +2657,7 @@
         <v>864.53</v>
       </c>
       <c r="AB23">
-        <v>987.9400000000001</v>
+        <v>987.94</v>
       </c>
       <c r="AC23" t="s">
         <v>30</v>
@@ -2649,7 +2669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2678,13 +2698,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>19.44</v>
+        <v>0.03</v>
       </c>
       <c r="K24">
-        <v>18.02</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>1037.36</v>
+        <v>1037.3599999999999</v>
       </c>
       <c r="M24">
         <v>895.64</v>
@@ -2729,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1037.36</v>
+        <v>1037.3599999999999</v>
       </c>
       <c r="AB24">
         <v>895.64</v>
@@ -2744,7 +2764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2773,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>18.08</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>19.17</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>818.33</v>
@@ -2839,7 +2859,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2868,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>26.95</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K26">
-        <v>24.54</v>
+        <v>0.09</v>
       </c>
       <c r="L26">
-        <v>1207.12</v>
+        <v>1207.1199999999999</v>
       </c>
       <c r="M26">
         <v>130.87</v>
@@ -2913,13 +2933,13 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z26">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="AA26">
-        <v>1207.12</v>
+        <v>1207.1199999999999</v>
       </c>
       <c r="AB26">
         <v>130.87</v>
@@ -2934,7 +2954,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2948,7 +2968,7 @@
         <v>44.45</v>
       </c>
       <c r="E27">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2963,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>18.65</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>18.83</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>987.1900000000001</v>
+        <v>987.19</v>
       </c>
       <c r="M27">
         <v>774.74</v>
@@ -2993,7 +3013,7 @@
         <v>44.45</v>
       </c>
       <c r="T27">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3014,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>987.1900000000001</v>
+        <v>987.19</v>
       </c>
       <c r="AB27">
         <v>774.74</v>
@@ -3029,7 +3049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3049,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H28">
         <v>0.06</v>
@@ -3058,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>27.07</v>
+        <v>0.33</v>
       </c>
       <c r="K28">
-        <v>36.82</v>
+        <v>0.36</v>
       </c>
       <c r="L28">
         <v>1205.49</v>
       </c>
       <c r="M28">
-        <v>306.53</v>
+        <v>306.52999999999997</v>
       </c>
       <c r="N28" t="s">
         <v>30</v>
@@ -3094,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W28">
         <v>0.06</v>
@@ -3103,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="Y28">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z28">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AA28">
         <v>1205.49</v>
       </c>
       <c r="AB28">
-        <v>306.53</v>
+        <v>306.52999999999997</v>
       </c>
       <c r="AC28" t="s">
         <v>30</v>
@@ -3124,7 +3144,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:31">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3153,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>19.07</v>
+        <v>0.05</v>
       </c>
       <c r="K29">
-        <v>17.87</v>
+        <v>0.01</v>
       </c>
       <c r="L29">
         <v>1268.83</v>
@@ -3219,7 +3239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3248,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>22.1</v>
+        <v>0.15</v>
       </c>
       <c r="K30">
-        <v>18.78</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>1365.63</v>
@@ -3314,7 +3334,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3325,7 +3345,7 @@
         <v>1.25</v>
       </c>
       <c r="D31">
-        <v>36.55</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="E31">
         <v>58.38</v>
@@ -3343,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>19.47</v>
+        <v>0.03</v>
       </c>
       <c r="K31">
-        <v>18.68</v>
+        <v>0.03</v>
       </c>
       <c r="L31">
         <v>1328.92</v>
       </c>
       <c r="M31">
-        <v>748.9299999999999</v>
+        <v>748.93</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -3370,7 +3390,7 @@
         <v>1.25</v>
       </c>
       <c r="S31">
-        <v>36.55</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="T31">
         <v>58.38</v>
@@ -3388,16 +3408,16 @@
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z31">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA31">
         <v>1328.92</v>
       </c>
       <c r="AB31">
-        <v>748.9299999999999</v>
+        <v>748.93</v>
       </c>
       <c r="AC31" t="s">
         <v>30</v>
@@ -3409,7 +3429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3420,7 +3440,7 @@
         <v>3.31</v>
       </c>
       <c r="D32">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="E32">
         <v>27.37</v>
@@ -3438,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>21.98</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K32">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>1439.07</v>
@@ -3465,7 +3485,7 @@
         <v>3.31</v>
       </c>
       <c r="S32">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="T32">
         <v>27.37</v>
@@ -3483,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="Y32">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3504,7 +3524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3533,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>19.04</v>
+        <v>0.02</v>
       </c>
       <c r="K33">
-        <v>17.82</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>1429.73</v>
@@ -3599,7 +3619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3607,7 +3627,7 @@
         <v>12578</v>
       </c>
       <c r="C34">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="D34">
         <v>23.23</v>
@@ -3628,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>20.81</v>
+        <v>0.11</v>
       </c>
       <c r="K34">
-        <v>17.69</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>1512.89</v>
@@ -3652,7 +3672,7 @@
         <v>12578</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="S34">
         <v>23.23</v>
@@ -3694,7 +3714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3714,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H35">
         <v>0.06</v>
@@ -3723,13 +3743,13 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>21.78</v>
+        <v>0.13</v>
       </c>
       <c r="K35">
-        <v>17.48</v>
+        <v>0.01</v>
       </c>
       <c r="L35">
-        <v>161.55</v>
+        <v>161.55000000000001</v>
       </c>
       <c r="M35">
         <v>144.4</v>
@@ -3759,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="V35">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W35">
         <v>0.06</v>
@@ -3768,13 +3788,13 @@
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z35">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AA35">
-        <v>161.55</v>
+        <v>161.55000000000001</v>
       </c>
       <c r="AB35">
         <v>144.4</v>
@@ -3789,7 +3809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3800,10 +3820,10 @@
         <v>3.42</v>
       </c>
       <c r="D36">
-        <v>36.48</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="E36">
-        <v>80.40000000000001</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3818,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>21.97</v>
+        <v>0.18</v>
       </c>
       <c r="K36">
-        <v>18.27</v>
+        <v>0</v>
       </c>
       <c r="L36">
         <v>231.65</v>
@@ -3845,10 +3865,10 @@
         <v>3.42</v>
       </c>
       <c r="S36">
-        <v>36.48</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="T36">
-        <v>80.40000000000001</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -3884,7 +3904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3898,7 +3918,7 @@
         <v>74.25</v>
       </c>
       <c r="E37">
-        <v>73.90000000000001</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3913,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>20.83</v>
+        <v>0.06</v>
       </c>
       <c r="K37">
-        <v>21.46</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L37">
         <v>477.34</v>
@@ -3943,7 +3963,7 @@
         <v>74.25</v>
       </c>
       <c r="T37">
-        <v>73.90000000000001</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -3979,7 +3999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3990,7 +4010,7 @@
         <v>3.83</v>
       </c>
       <c r="D38">
-        <v>37.66</v>
+        <v>37.659999999999997</v>
       </c>
       <c r="E38">
         <v>88.62</v>
@@ -4008,16 +4028,16 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>25.57</v>
+        <v>0.26</v>
       </c>
       <c r="K38">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>260.22</v>
+        <v>260.22000000000003</v>
       </c>
       <c r="M38">
-        <v>647.6799999999999</v>
+        <v>647.67999999999995</v>
       </c>
       <c r="N38" t="s">
         <v>30</v>
@@ -4035,7 +4055,7 @@
         <v>3.83</v>
       </c>
       <c r="S38">
-        <v>37.66</v>
+        <v>37.659999999999997</v>
       </c>
       <c r="T38">
         <v>88.62</v>
@@ -4059,10 +4079,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>260.22</v>
+        <v>260.22000000000003</v>
       </c>
       <c r="AB38">
-        <v>647.6799999999999</v>
+        <v>647.67999999999995</v>
       </c>
       <c r="AC38" t="s">
         <v>30</v>
@@ -4074,7 +4094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4103,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>19.97</v>
+        <v>0.04</v>
       </c>
       <c r="K39">
-        <v>17.72</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <v>93.8</v>
@@ -4169,7 +4189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4180,7 +4200,7 @@
         <v>3.48</v>
       </c>
       <c r="D40">
-        <v>33.62</v>
+        <v>33.619999999999997</v>
       </c>
       <c r="E40">
         <v>21.19</v>
@@ -4198,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>19.11</v>
+        <v>0.03</v>
       </c>
       <c r="K40">
-        <v>17.91</v>
+        <v>0</v>
       </c>
       <c r="L40">
         <v>199.78</v>
@@ -4225,7 +4245,7 @@
         <v>3.48</v>
       </c>
       <c r="S40">
-        <v>33.62</v>
+        <v>33.619999999999997</v>
       </c>
       <c r="T40">
         <v>21.19</v>
@@ -4264,7 +4284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4278,7 +4298,7 @@
         <v>40.32</v>
       </c>
       <c r="E41">
-        <v>64.59999999999999</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -4293,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>22.78</v>
+        <v>0.17</v>
       </c>
       <c r="K41">
-        <v>18.69</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>431.13</v>
@@ -4323,7 +4343,7 @@
         <v>40.32</v>
       </c>
       <c r="T41">
-        <v>64.59999999999999</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -4359,7 +4379,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4367,7 +4387,7 @@
         <v>43203</v>
       </c>
       <c r="C42">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="D42">
         <v>17.84</v>
@@ -4388,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>22.27</v>
+        <v>0.12</v>
       </c>
       <c r="K42">
-        <v>18.63</v>
+        <v>0.01</v>
       </c>
       <c r="L42">
         <v>523.03</v>
@@ -4412,7 +4432,7 @@
         <v>43203</v>
       </c>
       <c r="R42">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="S42">
         <v>17.84</v>
@@ -4454,7 +4474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4468,13 +4488,13 @@
         <v>53.85</v>
       </c>
       <c r="E43">
-        <v>76.59999999999999</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H43">
         <v>0.06</v>
@@ -4483,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>24.38</v>
+        <v>0.25</v>
       </c>
       <c r="K43">
-        <v>18.59</v>
+        <v>0</v>
       </c>
       <c r="L43">
         <v>560.88</v>
@@ -4513,13 +4533,13 @@
         <v>53.85</v>
       </c>
       <c r="T43">
-        <v>76.59999999999999</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="U43">
         <v>0</v>
       </c>
       <c r="V43">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W43">
         <v>0.06</v>
@@ -4549,7 +4569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:31">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4578,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>23.4</v>
+        <v>0.15</v>
       </c>
       <c r="K44">
-        <v>20.88</v>
+        <v>0.01</v>
       </c>
       <c r="L44">
         <v>677.91</v>
@@ -4644,7 +4664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4652,7 +4672,7 @@
         <v>42820</v>
       </c>
       <c r="C45">
-        <v>8.029999999999999</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="D45">
         <v>71.92</v>
@@ -4673,16 +4693,16 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>21.33</v>
+        <v>0.09</v>
       </c>
       <c r="K45">
-        <v>20.01</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <v>747.8</v>
       </c>
       <c r="M45">
-        <v>603.95</v>
+        <v>603.95000000000005</v>
       </c>
       <c r="N45" t="s">
         <v>30</v>
@@ -4697,7 +4717,7 @@
         <v>42820</v>
       </c>
       <c r="R45">
-        <v>8.029999999999999</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="S45">
         <v>71.92</v>
@@ -4727,7 +4747,7 @@
         <v>747.8</v>
       </c>
       <c r="AB45">
-        <v>603.95</v>
+        <v>603.95000000000005</v>
       </c>
       <c r="AC45" t="s">
         <v>30</v>
@@ -4739,7 +4759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4768,16 +4788,16 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>28.07</v>
+        <v>0.49</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>616.58</v>
+        <v>616.58000000000004</v>
       </c>
       <c r="M46">
-        <v>79.48999999999999</v>
+        <v>79.489999999999995</v>
       </c>
       <c r="N46" t="s">
         <v>30</v>
@@ -4819,10 +4839,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>616.58</v>
+        <v>616.58000000000004</v>
       </c>
       <c r="AB46">
-        <v>79.48999999999999</v>
+        <v>79.489999999999995</v>
       </c>
       <c r="AC46" t="s">
         <v>30</v>
@@ -4834,7 +4854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4863,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>26.77</v>
+        <v>0.25</v>
       </c>
       <c r="K47">
-        <v>19.15</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>899.0700000000001</v>
+        <v>899.07</v>
       </c>
       <c r="M47">
         <v>852.77</v>
@@ -4914,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>899.0700000000001</v>
+        <v>899.07</v>
       </c>
       <c r="AB47">
         <v>852.77</v>
@@ -4929,7 +4949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4958,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>22.6</v>
+        <v>0.13</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4967,7 +4987,7 @@
         <v>607.09</v>
       </c>
       <c r="M48">
-        <v>299.29</v>
+        <v>299.29000000000002</v>
       </c>
       <c r="N48" t="s">
         <v>30</v>
@@ -5012,7 +5032,7 @@
         <v>607.09</v>
       </c>
       <c r="AB48">
-        <v>299.29</v>
+        <v>299.29000000000002</v>
       </c>
       <c r="AC48" t="s">
         <v>30</v>
@@ -5024,7 +5044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:31">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5053,10 +5073,10 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>25.58</v>
+        <v>0.22</v>
       </c>
       <c r="K49">
-        <v>31.33</v>
+        <v>0.33</v>
       </c>
       <c r="L49">
         <v>1053.76</v>
@@ -5098,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5119,7 +5139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5148,13 +5168,13 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>29.82</v>
+        <v>0.51</v>
       </c>
       <c r="K50">
-        <v>25.32</v>
+        <v>0.26</v>
       </c>
       <c r="L50">
-        <v>882.0599999999999</v>
+        <v>882.06</v>
       </c>
       <c r="M50">
         <v>60.16</v>
@@ -5193,13 +5213,13 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="Z50">
-        <v>0.12</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA50">
-        <v>882.0599999999999</v>
+        <v>882.06</v>
       </c>
       <c r="AB50">
         <v>60.16</v>
@@ -5214,7 +5234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -5243,10 +5263,10 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>21.12</v>
+        <v>0.08</v>
       </c>
       <c r="K51">
-        <v>18.46</v>
+        <v>0</v>
       </c>
       <c r="L51">
         <v>1005.51</v>
@@ -5309,7 +5329,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -5317,7 +5337,7 @@
         <v>53101</v>
       </c>
       <c r="C52">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="D52">
         <v>50.25</v>
@@ -5338,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>23.53</v>
+        <v>0.22</v>
       </c>
       <c r="K52">
-        <v>20.18</v>
+        <v>0</v>
       </c>
       <c r="L52">
         <v>1108.67</v>
@@ -5362,7 +5382,7 @@
         <v>53101</v>
       </c>
       <c r="R52">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="S52">
         <v>50.25</v>
@@ -5404,7 +5424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:31">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -5433,16 +5453,16 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>30.52</v>
+        <v>0.34</v>
       </c>
       <c r="K53">
-        <v>22.4</v>
+        <v>0.19</v>
       </c>
       <c r="L53">
         <v>1224.44</v>
       </c>
       <c r="M53">
-        <v>650.0599999999999</v>
+        <v>650.05999999999995</v>
       </c>
       <c r="N53" t="s">
         <v>30</v>
@@ -5487,7 +5507,7 @@
         <v>1224.44</v>
       </c>
       <c r="AB53">
-        <v>650.0599999999999</v>
+        <v>650.05999999999995</v>
       </c>
       <c r="AC53" t="s">
         <v>30</v>
@@ -5499,7 +5519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -5528,10 +5548,10 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>30.39</v>
+        <v>0.39</v>
       </c>
       <c r="K54">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L54">
         <v>1165.22</v>
@@ -5594,7 +5614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -5605,7 +5625,7 @@
         <v>3.63</v>
       </c>
       <c r="D55">
-        <v>39.62</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="E55">
         <v>50.57</v>
@@ -5623,13 +5643,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>25.36</v>
+        <v>0.17</v>
       </c>
       <c r="K55">
-        <v>23.85</v>
+        <v>0.08</v>
       </c>
       <c r="L55">
-        <v>1255.14</v>
+        <v>1255.1400000000001</v>
       </c>
       <c r="M55">
         <v>878.85</v>
@@ -5650,7 +5670,7 @@
         <v>3.63</v>
       </c>
       <c r="S55">
-        <v>39.62</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="T55">
         <v>50.57</v>
@@ -5674,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>1255.14</v>
+        <v>1255.1400000000001</v>
       </c>
       <c r="AB55">
         <v>878.85</v>
@@ -5689,7 +5709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:31">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -5709,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="H56">
         <v>0.31</v>
@@ -5718,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>21.14</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K56">
-        <v>19.78</v>
+        <v>0</v>
       </c>
       <c r="L56">
         <v>1417.01</v>
@@ -5754,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="V56">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="W56">
         <v>0.31</v>
@@ -5784,7 +5804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:31">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -5813,10 +5833,10 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>26.16</v>
+        <v>0.33</v>
       </c>
       <c r="K57">
-        <v>21.48</v>
+        <v>0.05</v>
       </c>
       <c r="L57">
         <v>1440.29</v>
@@ -5879,7 +5899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:31">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -5908,10 +5928,10 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>31.69</v>
+        <v>0.46</v>
       </c>
       <c r="K58">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L58">
         <v>1457.64</v>
@@ -5974,7 +5994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:31">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6003,10 +6023,10 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>21.76</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K59">
-        <v>20.07</v>
+        <v>0</v>
       </c>
       <c r="L59">
         <v>1462.7</v>
@@ -6069,7 +6089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:31">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6098,10 +6118,10 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>20.53</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K60">
-        <v>18.73</v>
+        <v>0</v>
       </c>
       <c r="L60">
         <v>1453.72</v>
@@ -6164,7 +6184,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:31">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6172,7 +6192,7 @@
         <v>43433</v>
       </c>
       <c r="C61">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="D61">
         <v>28.63</v>
@@ -6193,13 +6213,13 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>23.74</v>
+        <v>0.18</v>
       </c>
       <c r="K61">
-        <v>17.83</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>257.22</v>
+        <v>257.22000000000003</v>
       </c>
       <c r="M61">
         <v>336.06</v>
@@ -6217,7 +6237,7 @@
         <v>43433</v>
       </c>
       <c r="R61">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="S61">
         <v>28.63</v>
@@ -6244,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>257.22</v>
+        <v>257.22000000000003</v>
       </c>
       <c r="AB61">
         <v>336.06</v>
@@ -6259,7 +6279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:31">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6288,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>25.03</v>
+        <v>0.33</v>
       </c>
       <c r="K62">
-        <v>25.83</v>
+        <v>0.3</v>
       </c>
       <c r="L62">
         <v>52.69</v>
@@ -6354,7 +6374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:31">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6383,16 +6403,16 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>31.87</v>
+        <v>0.45</v>
       </c>
       <c r="K63">
-        <v>27.62</v>
+        <v>0.32</v>
       </c>
       <c r="L63">
         <v>88.13</v>
       </c>
       <c r="M63">
-        <v>587.55</v>
+        <v>587.54999999999995</v>
       </c>
       <c r="N63" t="s">
         <v>30</v>
@@ -6428,16 +6448,16 @@
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z63">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="AA63">
         <v>88.13</v>
       </c>
       <c r="AB63">
-        <v>587.55</v>
+        <v>587.54999999999995</v>
       </c>
       <c r="AC63" t="s">
         <v>30</v>
@@ -6449,7 +6469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:31">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6469,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H64">
         <v>0.06</v>
@@ -6478,10 +6498,10 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>19.77</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K64">
-        <v>18.02</v>
+        <v>0</v>
       </c>
       <c r="L64">
         <v>189.24</v>
@@ -6514,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="V64">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W64">
         <v>0.06</v>
@@ -6544,7 +6564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6552,10 +6572,10 @@
         <v>6338</v>
       </c>
       <c r="C65">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D65">
-        <v>8.789999999999999</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="E65">
         <v>7.34</v>
@@ -6567,16 +6587,16 @@
         <v>0.71</v>
       </c>
       <c r="H65">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I65">
         <v>0</v>
       </c>
       <c r="J65">
-        <v>17.47</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>17.35</v>
+        <v>0</v>
       </c>
       <c r="L65">
         <v>58.44</v>
@@ -6597,10 +6617,10 @@
         <v>6338</v>
       </c>
       <c r="R65">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="S65">
-        <v>8.789999999999999</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="T65">
         <v>7.34</v>
@@ -6612,7 +6632,7 @@
         <v>0.71</v>
       </c>
       <c r="W65">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X65">
         <v>0</v>
@@ -6639,7 +6659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6668,10 +6688,10 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>17.95</v>
+        <v>0.01</v>
       </c>
       <c r="K66">
-        <v>17.53</v>
+        <v>0</v>
       </c>
       <c r="L66">
         <v>160.29</v>
@@ -6734,7 +6754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:31">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6745,7 +6765,7 @@
         <v>6.38</v>
       </c>
       <c r="D67">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="E67">
         <v>44.22</v>
@@ -6763,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>20.38</v>
+        <v>0.08</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -6790,7 +6810,7 @@
         <v>6.38</v>
       </c>
       <c r="S67">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="T67">
         <v>44.22</v>
@@ -6829,7 +6849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6840,7 +6860,7 @@
         <v>5.63</v>
       </c>
       <c r="D68">
-        <v>37.34</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="E68">
         <v>42.83</v>
@@ -6849,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H68">
         <v>0.19</v>
@@ -6858,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>20.39</v>
+        <v>0.05</v>
       </c>
       <c r="K68">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="L68">
         <v>308.18</v>
@@ -6885,7 +6905,7 @@
         <v>5.63</v>
       </c>
       <c r="S68">
-        <v>37.34</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="T68">
         <v>42.83</v>
@@ -6894,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="V68">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="W68">
         <v>0.19</v>
@@ -6924,7 +6944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6932,7 +6952,7 @@
         <v>64346</v>
       </c>
       <c r="C69">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="D69">
         <v>27.35</v>
@@ -6953,10 +6973,10 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>20.53</v>
+        <v>0.08</v>
       </c>
       <c r="K69">
-        <v>18.26</v>
+        <v>0</v>
       </c>
       <c r="L69">
         <v>364.33</v>
@@ -6977,7 +6997,7 @@
         <v>64346</v>
       </c>
       <c r="R69">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="S69">
         <v>27.35</v>
@@ -7019,7 +7039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -7048,16 +7068,16 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>29.28</v>
+        <v>0.36</v>
       </c>
       <c r="K70">
-        <v>20.49</v>
+        <v>0.04</v>
       </c>
       <c r="L70">
-        <v>303.53</v>
+        <v>303.52999999999997</v>
       </c>
       <c r="M70">
-        <v>82.40000000000001</v>
+        <v>82.4</v>
       </c>
       <c r="N70" t="s">
         <v>30</v>
@@ -7099,10 +7119,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>303.53</v>
+        <v>303.52999999999997</v>
       </c>
       <c r="AB70">
-        <v>82.40000000000001</v>
+        <v>82.4</v>
       </c>
       <c r="AC70" t="s">
         <v>30</v>
@@ -7114,7 +7134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:31">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7143,10 +7163,10 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>20.01</v>
+        <v>0.03</v>
       </c>
       <c r="K71">
-        <v>19.55</v>
+        <v>0</v>
       </c>
       <c r="L71">
         <v>553.28</v>
@@ -7209,7 +7229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7223,7 +7243,7 @@
         <v>52.36</v>
       </c>
       <c r="E72">
-        <v>76.73999999999999</v>
+        <v>76.739999999999995</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -7238,10 +7258,10 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>19.2</v>
+        <v>0.01</v>
       </c>
       <c r="K72">
-        <v>18.67</v>
+        <v>0</v>
       </c>
       <c r="L72">
         <v>499.4</v>
@@ -7268,7 +7288,7 @@
         <v>52.36</v>
       </c>
       <c r="T72">
-        <v>76.73999999999999</v>
+        <v>76.739999999999995</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -7304,7 +7324,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7333,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>23.8</v>
+        <v>0.15</v>
       </c>
       <c r="K73">
-        <v>60.63</v>
+        <v>0.92</v>
       </c>
       <c r="L73">
         <v>635.09</v>
@@ -7378,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="Y73">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7399,7 +7419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -7413,7 +7433,7 @@
         <v>53.11</v>
       </c>
       <c r="E74">
-        <v>71.20999999999999</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -7428,16 +7448,16 @@
         <v>0</v>
       </c>
       <c r="J74">
-        <v>21.3</v>
+        <v>0.08</v>
       </c>
       <c r="K74">
-        <v>19.78</v>
+        <v>0</v>
       </c>
       <c r="L74">
         <v>812.72</v>
       </c>
       <c r="M74">
-        <v>636.4299999999999</v>
+        <v>636.42999999999995</v>
       </c>
       <c r="N74" t="s">
         <v>30</v>
@@ -7458,7 +7478,7 @@
         <v>53.11</v>
       </c>
       <c r="T74">
-        <v>71.20999999999999</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -7482,7 +7502,7 @@
         <v>812.72</v>
       </c>
       <c r="AB74">
-        <v>636.4299999999999</v>
+        <v>636.42999999999995</v>
       </c>
       <c r="AC74" t="s">
         <v>30</v>
@@ -7494,7 +7514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7523,16 +7543,16 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <v>21.85</v>
+        <v>0.11</v>
       </c>
       <c r="K75">
         <v>0</v>
       </c>
       <c r="L75">
-        <v>554.42</v>
+        <v>554.41999999999996</v>
       </c>
       <c r="M75">
-        <v>548.42</v>
+        <v>548.41999999999996</v>
       </c>
       <c r="N75" t="s">
         <v>30</v>
@@ -7574,10 +7594,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>554.42</v>
+        <v>554.41999999999996</v>
       </c>
       <c r="AB75">
-        <v>548.42</v>
+        <v>548.41999999999996</v>
       </c>
       <c r="AC75" t="s">
         <v>30</v>
@@ -7589,7 +7609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -7600,16 +7620,16 @@
         <v>5.95</v>
       </c>
       <c r="D76">
-        <v>67.34999999999999</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="E76">
-        <v>77.34999999999999</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H76">
         <v>0.06</v>
@@ -7618,10 +7638,10 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <v>24.55</v>
+        <v>0.17</v>
       </c>
       <c r="K76">
-        <v>24.01</v>
+        <v>0.23</v>
       </c>
       <c r="L76">
         <v>775.51</v>
@@ -7645,16 +7665,16 @@
         <v>5.95</v>
       </c>
       <c r="S76">
-        <v>67.34999999999999</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="T76">
-        <v>77.34999999999999</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="U76">
         <v>0</v>
       </c>
       <c r="V76">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W76">
         <v>0.06</v>
@@ -7663,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,7 +7704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -7713,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="J77">
-        <v>21.06</v>
+        <v>0.08</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -7779,7 +7799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7790,10 +7810,10 @@
         <v>4.22</v>
       </c>
       <c r="D78">
-        <v>67.45999999999999</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="E78">
-        <v>68.59999999999999</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -7808,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <v>22.15</v>
+        <v>0.08</v>
       </c>
       <c r="K78">
-        <v>47.62</v>
+        <v>0.53</v>
       </c>
       <c r="L78">
         <v>1090.19</v>
@@ -7835,10 +7855,10 @@
         <v>4.22</v>
       </c>
       <c r="S78">
-        <v>67.45999999999999</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="T78">
-        <v>68.59999999999999</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -7874,7 +7894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7903,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="J79">
-        <v>19.49</v>
+        <v>0.02</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -7969,7 +7989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7998,10 +8018,10 @@
         <v>0</v>
       </c>
       <c r="J80">
-        <v>22.75</v>
+        <v>0.16</v>
       </c>
       <c r="K80">
-        <v>28.78</v>
+        <v>0.78</v>
       </c>
       <c r="L80">
         <v>1078.19</v>
@@ -8064,7 +8084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:31">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -8093,10 +8113,10 @@
         <v>0</v>
       </c>
       <c r="J81">
-        <v>22.76</v>
+        <v>0.16</v>
       </c>
       <c r="K81">
-        <v>20.18</v>
+        <v>0</v>
       </c>
       <c r="L81">
         <v>1091.47</v>
@@ -8159,7 +8179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -8188,13 +8208,13 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>25.33</v>
+        <v>0.25</v>
       </c>
       <c r="K82">
-        <v>19.45</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>1217.84</v>
+        <v>1217.8399999999999</v>
       </c>
       <c r="M82">
         <v>274.81</v>
@@ -8239,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1217.84</v>
+        <v>1217.8399999999999</v>
       </c>
       <c r="AB82">
         <v>274.81</v>
@@ -8254,7 +8274,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:31">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -8268,7 +8288,7 @@
         <v>22.65</v>
       </c>
       <c r="E83">
-        <v>35.62</v>
+        <v>35.619999999999997</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -8283,10 +8303,10 @@
         <v>0</v>
       </c>
       <c r="J83">
-        <v>22.21</v>
+        <v>0.08</v>
       </c>
       <c r="K83">
-        <v>19.07</v>
+        <v>0.01</v>
       </c>
       <c r="L83">
         <v>1303.74</v>
@@ -8313,7 +8333,7 @@
         <v>22.65</v>
       </c>
       <c r="T83">
-        <v>35.62</v>
+        <v>35.619999999999997</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -8328,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8349,7 +8369,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:31">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -8357,10 +8377,10 @@
         <v>15485</v>
       </c>
       <c r="C84">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D84">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="E84">
         <v>22.21</v>
@@ -8378,10 +8398,10 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>21.97</v>
+        <v>0.18</v>
       </c>
       <c r="K84">
-        <v>18.17</v>
+        <v>0</v>
       </c>
       <c r="L84">
         <v>1238.2</v>
@@ -8402,10 +8422,10 @@
         <v>15485</v>
       </c>
       <c r="R84">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="S84">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="T84">
         <v>22.21</v>
@@ -8444,7 +8464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:31">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -8473,16 +8493,16 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>23.11</v>
+        <v>0.1</v>
       </c>
       <c r="K85">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L85">
         <v>1361.61</v>
       </c>
       <c r="M85">
-        <v>558.3200000000001</v>
+        <v>558.32000000000005</v>
       </c>
       <c r="N85" t="s">
         <v>30</v>
@@ -8518,7 +8538,7 @@
         <v>0</v>
       </c>
       <c r="Y85">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8527,7 +8547,7 @@
         <v>1361.61</v>
       </c>
       <c r="AB85">
-        <v>558.3200000000001</v>
+        <v>558.32000000000005</v>
       </c>
       <c r="AC85" t="s">
         <v>30</v>
@@ -8539,7 +8559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:31">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -8553,7 +8573,7 @@
         <v>49.67</v>
       </c>
       <c r="E86">
-        <v>78.26000000000001</v>
+        <v>78.260000000000005</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -8568,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>20.97</v>
+        <v>0.05</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -8598,7 +8618,7 @@
         <v>49.67</v>
       </c>
       <c r="T86">
-        <v>78.26000000000001</v>
+        <v>78.260000000000005</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -8634,7 +8654,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:31">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -8648,7 +8668,7 @@
         <v>37.15</v>
       </c>
       <c r="E87">
-        <v>39.09</v>
+        <v>39.090000000000003</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -8663,10 +8683,10 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>26.3</v>
+        <v>0.18</v>
       </c>
       <c r="K87">
-        <v>30.83</v>
+        <v>0.37</v>
       </c>
       <c r="L87">
         <v>1475.5</v>
@@ -8693,7 +8713,7 @@
         <v>37.15</v>
       </c>
       <c r="T87">
-        <v>39.09</v>
+        <v>39.090000000000003</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -8708,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="Y87">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8729,7 +8749,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:31">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -8737,7 +8757,7 @@
         <v>33863</v>
       </c>
       <c r="C88">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D88">
         <v>31.02</v>
@@ -8758,10 +8778,10 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>22.59</v>
+        <v>0.09</v>
       </c>
       <c r="K88">
-        <v>19.29</v>
+        <v>0.02</v>
       </c>
       <c r="L88">
         <v>1487.5</v>
@@ -8782,7 +8802,7 @@
         <v>33863</v>
       </c>
       <c r="R88">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="S88">
         <v>31.02</v>
@@ -8824,7 +8844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:31">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -8853,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>22.17</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K89">
-        <v>19.18</v>
+        <v>0.02</v>
       </c>
       <c r="L89">
         <v>1495.21</v>
@@ -8919,7 +8939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:31">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -8948,10 +8968,10 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>20.18</v>
+        <v>0.01</v>
       </c>
       <c r="K90">
-        <v>19.51</v>
+        <v>0</v>
       </c>
       <c r="L90">
         <v>1512.51</v>
@@ -9014,7 +9034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:31">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -9043,10 +9063,10 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>19.77</v>
+        <v>0.03</v>
       </c>
       <c r="K91">
-        <v>18.84</v>
+        <v>0</v>
       </c>
       <c r="L91">
         <v>1510.65</v>
@@ -9109,7 +9129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:31">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -9138,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <v>17.42</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="L92">
         <v>83.55</v>
@@ -9204,7 +9224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:31">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -9233,10 +9253,10 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <v>21.86</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K93">
-        <v>18.62</v>
+        <v>0</v>
       </c>
       <c r="L93">
         <v>298.51</v>
@@ -9299,7 +9319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:31">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -9313,7 +9333,7 @@
         <v>67.14</v>
       </c>
       <c r="E94">
-        <v>86.98999999999999</v>
+        <v>86.99</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -9328,10 +9348,10 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <v>24.74</v>
+        <v>0.19</v>
       </c>
       <c r="K94">
-        <v>35.62</v>
+        <v>0.3</v>
       </c>
       <c r="L94">
         <v>600.59</v>
@@ -9358,7 +9378,7 @@
         <v>67.14</v>
       </c>
       <c r="T94">
-        <v>86.98999999999999</v>
+        <v>86.99</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -9373,10 +9393,10 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z94">
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA94">
         <v>600.59</v>
@@ -9394,7 +9414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:31">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -9423,10 +9443,10 @@
         <v>0</v>
       </c>
       <c r="J95">
-        <v>19.08</v>
+        <v>0</v>
       </c>
       <c r="K95">
-        <v>19.36</v>
+        <v>0</v>
       </c>
       <c r="L95">
         <v>190.07</v>
@@ -9468,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="Y95">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z95">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="AA95">
         <v>190.07</v>
@@ -9489,7 +9509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:31">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -9518,10 +9538,10 @@
         <v>0</v>
       </c>
       <c r="J96">
-        <v>28.57</v>
+        <v>0.26</v>
       </c>
       <c r="K96">
-        <v>41.86</v>
+        <v>0.54</v>
       </c>
       <c r="L96">
         <v>248.98</v>
@@ -9563,10 +9583,10 @@
         <v>0</v>
       </c>
       <c r="Y96">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z96">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="AA96">
         <v>248.98</v>
@@ -9584,7 +9604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:31">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -9595,7 +9615,7 @@
         <v>2.68</v>
       </c>
       <c r="D97">
-        <v>39.87</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="E97">
         <v>25.73</v>
@@ -9613,16 +9633,16 @@
         <v>0</v>
       </c>
       <c r="J97">
-        <v>27.72</v>
+        <v>0.3</v>
       </c>
       <c r="K97">
-        <v>21.21</v>
+        <v>0.09</v>
       </c>
       <c r="L97">
         <v>213.87</v>
       </c>
       <c r="M97">
-        <v>823.6900000000001</v>
+        <v>823.69</v>
       </c>
       <c r="N97" t="s">
         <v>30</v>
@@ -9640,7 +9660,7 @@
         <v>2.68</v>
       </c>
       <c r="S97">
-        <v>39.87</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="T97">
         <v>25.73</v>
@@ -9658,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="Y97">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9667,7 +9687,7 @@
         <v>213.87</v>
       </c>
       <c r="AB97">
-        <v>823.6900000000001</v>
+        <v>823.69</v>
       </c>
       <c r="AC97" t="s">
         <v>30</v>
@@ -9679,7 +9699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:31">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -9708,10 +9728,10 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>19.85</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K98">
-        <v>17.67</v>
+        <v>0.01</v>
       </c>
       <c r="L98">
         <v>178.51</v>
@@ -9774,7 +9794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:31">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -9803,10 +9823,10 @@
         <v>0</v>
       </c>
       <c r="J99">
-        <v>26.87</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K99">
-        <v>20.98</v>
+        <v>0.08</v>
       </c>
       <c r="L99">
         <v>600.64</v>
@@ -9848,10 +9868,10 @@
         <v>0</v>
       </c>
       <c r="Y99">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z99">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AA99">
         <v>600.64</v>
@@ -9869,7 +9889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:31">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -9898,10 +9918,10 @@
         <v>0</v>
       </c>
       <c r="J100">
-        <v>24.65</v>
+        <v>0.11</v>
       </c>
       <c r="K100">
-        <v>80.48</v>
+        <v>0.85</v>
       </c>
       <c r="L100">
         <v>462.49</v>
@@ -9964,7 +9984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:31">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -9972,13 +9992,13 @@
         <v>8786</v>
       </c>
       <c r="C101">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="D101">
         <v>123.74</v>
       </c>
       <c r="E101">
-        <v>131.67</v>
+        <v>131.66999999999999</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -9993,16 +10013,16 @@
         <v>0</v>
       </c>
       <c r="J101">
-        <v>22.3</v>
+        <v>0.15</v>
       </c>
       <c r="K101">
-        <v>20.81</v>
+        <v>0.02</v>
       </c>
       <c r="L101">
         <v>459.54</v>
       </c>
       <c r="M101">
-        <v>514.4299999999999</v>
+        <v>514.42999999999995</v>
       </c>
       <c r="N101" t="s">
         <v>30</v>
@@ -10017,13 +10037,13 @@
         <v>8786</v>
       </c>
       <c r="R101">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="S101">
         <v>123.74</v>
       </c>
       <c r="T101">
-        <v>131.67</v>
+        <v>131.66999999999999</v>
       </c>
       <c r="U101">
         <v>0</v>
@@ -10038,16 +10058,16 @@
         <v>0</v>
       </c>
       <c r="Y101">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z101">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="AA101">
         <v>459.54</v>
       </c>
       <c r="AB101">
-        <v>514.4299999999999</v>
+        <v>514.42999999999995</v>
       </c>
       <c r="AC101" t="s">
         <v>30</v>
@@ -10059,7 +10079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:31">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -10073,13 +10093,13 @@
         <v>50.07</v>
       </c>
       <c r="E102">
-        <v>72.68000000000001</v>
+        <v>72.680000000000007</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H102">
         <v>0.06</v>
@@ -10088,10 +10108,10 @@
         <v>0</v>
       </c>
       <c r="J102">
-        <v>24</v>
+        <v>0.11</v>
       </c>
       <c r="K102">
-        <v>21.19</v>
+        <v>0.05</v>
       </c>
       <c r="L102">
         <v>926.49</v>
@@ -10118,13 +10138,13 @@
         <v>50.07</v>
       </c>
       <c r="T102">
-        <v>72.68000000000001</v>
+        <v>72.680000000000007</v>
       </c>
       <c r="U102">
         <v>0</v>
       </c>
       <c r="V102">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W102">
         <v>0.06</v>
@@ -10133,7 +10153,7 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z102">
         <v>0</v>
@@ -10154,7 +10174,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:31">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -10174,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G103">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H103">
         <v>0.43</v>
@@ -10183,10 +10203,10 @@
         <v>0</v>
       </c>
       <c r="J103">
-        <v>26.99</v>
+        <v>0.27</v>
       </c>
       <c r="K103">
-        <v>21.98</v>
+        <v>0.09</v>
       </c>
       <c r="L103">
         <v>785.2</v>
@@ -10219,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="V103">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="W103">
         <v>0.43</v>
@@ -10228,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z103">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AA103">
         <v>785.2</v>
@@ -10249,7 +10269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:31">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -10263,7 +10283,7 @@
         <v>79.48</v>
       </c>
       <c r="E104">
-        <v>97.26000000000001</v>
+        <v>97.26</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -10278,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <v>22.82</v>
+        <v>0.13</v>
       </c>
       <c r="K104">
-        <v>21.69</v>
+        <v>0.06</v>
       </c>
       <c r="L104">
         <v>592.61</v>
@@ -10308,7 +10328,7 @@
         <v>79.48</v>
       </c>
       <c r="T104">
-        <v>97.26000000000001</v>
+        <v>97.26</v>
       </c>
       <c r="U104">
         <v>0</v>
@@ -10344,7 +10364,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:31">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -10373,13 +10393,13 @@
         <v>0</v>
       </c>
       <c r="J105">
-        <v>22.65</v>
+        <v>0.11</v>
       </c>
       <c r="K105">
-        <v>47.93</v>
+        <v>0.53</v>
       </c>
       <c r="L105">
-        <v>816.8099999999999</v>
+        <v>816.81</v>
       </c>
       <c r="M105">
         <v>654.37</v>
@@ -10418,13 +10438,13 @@
         <v>0</v>
       </c>
       <c r="Y105">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z105">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AA105">
-        <v>816.8099999999999</v>
+        <v>816.81</v>
       </c>
       <c r="AB105">
         <v>654.37</v>
@@ -10439,7 +10459,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:31">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -10453,7 +10473,7 @@
         <v>56.57</v>
       </c>
       <c r="E106">
-        <v>86.48999999999999</v>
+        <v>86.49</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -10462,16 +10482,16 @@
         <v>0.93</v>
       </c>
       <c r="H106">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I106">
         <v>0</v>
       </c>
       <c r="J106">
-        <v>21.45</v>
+        <v>0.08</v>
       </c>
       <c r="K106">
-        <v>42.01</v>
+        <v>0.38</v>
       </c>
       <c r="L106">
         <v>972.27</v>
@@ -10498,7 +10518,7 @@
         <v>56.57</v>
       </c>
       <c r="T106">
-        <v>86.48999999999999</v>
+        <v>86.49</v>
       </c>
       <c r="U106">
         <v>0</v>
@@ -10507,7 +10527,7 @@
         <v>0.93</v>
       </c>
       <c r="W106">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X106">
         <v>0</v>
@@ -10534,7 +10554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:31">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -10548,7 +10568,7 @@
         <v>48.83</v>
       </c>
       <c r="E107">
-        <v>70.68000000000001</v>
+        <v>70.680000000000007</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -10563,10 +10583,10 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>24.26</v>
+        <v>0.12</v>
       </c>
       <c r="K107">
-        <v>20.77</v>
+        <v>0.05</v>
       </c>
       <c r="L107">
         <v>1216.05</v>
@@ -10593,7 +10613,7 @@
         <v>48.83</v>
       </c>
       <c r="T107">
-        <v>70.68000000000001</v>
+        <v>70.680000000000007</v>
       </c>
       <c r="U107">
         <v>0</v>
@@ -10629,7 +10649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:31">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -10643,7 +10663,7 @@
         <v>58.73</v>
       </c>
       <c r="E108">
-        <v>94.01000000000001</v>
+        <v>94.01</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -10658,10 +10678,10 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>21.39</v>
+        <v>0.03</v>
       </c>
       <c r="K108">
-        <v>20.9</v>
+        <v>0.01</v>
       </c>
       <c r="L108">
         <v>731.23</v>
@@ -10688,7 +10708,7 @@
         <v>58.73</v>
       </c>
       <c r="T108">
-        <v>94.01000000000001</v>
+        <v>94.01</v>
       </c>
       <c r="U108">
         <v>0</v>
@@ -10724,7 +10744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:31">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -10753,10 +10773,10 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <v>29.84</v>
+        <v>0.27</v>
       </c>
       <c r="K109">
-        <v>28.98</v>
+        <v>0.22</v>
       </c>
       <c r="L109">
         <v>959.87</v>
@@ -10798,10 +10818,10 @@
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Z109">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="AA109">
         <v>959.87</v>
@@ -10819,7 +10839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:31">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -10827,7 +10847,7 @@
         <v>49877</v>
       </c>
       <c r="C110">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="D110">
         <v>51.29</v>
@@ -10848,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <v>29.26</v>
+        <v>0.42</v>
       </c>
       <c r="K110">
-        <v>22.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L110">
         <v>1249.27</v>
@@ -10872,7 +10892,7 @@
         <v>49877</v>
       </c>
       <c r="R110">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="S110">
         <v>51.29</v>
@@ -10914,7 +10934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:31">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -10937,19 +10957,19 @@
         <v>0.72</v>
       </c>
       <c r="H111">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I111">
         <v>0</v>
       </c>
       <c r="J111">
-        <v>20.79</v>
+        <v>0.11</v>
       </c>
       <c r="K111">
-        <v>22.77</v>
+        <v>0.18</v>
       </c>
       <c r="L111">
-        <v>1105.39</v>
+        <v>1105.3900000000001</v>
       </c>
       <c r="M111">
         <v>970.24</v>
@@ -10982,19 +11002,19 @@
         <v>0.72</v>
       </c>
       <c r="W111">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X111">
         <v>0</v>
       </c>
       <c r="Y111">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z111">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AA111">
-        <v>1105.39</v>
+        <v>1105.3900000000001</v>
       </c>
       <c r="AB111">
         <v>970.24</v>
@@ -11009,7 +11029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:31">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -11038,10 +11058,10 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <v>19.96</v>
+        <v>0.03</v>
       </c>
       <c r="K112">
-        <v>18.88</v>
+        <v>0</v>
       </c>
       <c r="L112">
         <v>1368.31</v>
@@ -11104,7 +11124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:31">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -11133,10 +11153,10 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>18.7</v>
+        <v>0.01</v>
       </c>
       <c r="K113">
-        <v>18.27</v>
+        <v>0.01</v>
       </c>
       <c r="L113">
         <v>1356.29</v>
@@ -11178,10 +11198,10 @@
         <v>0</v>
       </c>
       <c r="Y113">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z113">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AA113">
         <v>1356.29</v>
@@ -11199,7 +11219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:31">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -11228,10 +11248,10 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>24.97</v>
+        <v>0.18</v>
       </c>
       <c r="K114">
-        <v>21.63</v>
+        <v>0.1</v>
       </c>
       <c r="L114">
         <v>1410.74</v>
@@ -11276,7 +11296,7 @@
         <v>0</v>
       </c>
       <c r="Z114">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AA114">
         <v>1410.74</v>
@@ -11294,7 +11314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:31">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -11302,7 +11322,7 @@
         <v>15898</v>
       </c>
       <c r="C115">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="D115">
         <v>46.64</v>
@@ -11317,16 +11337,16 @@
         <v>0.86</v>
       </c>
       <c r="H115">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I115">
         <v>0</v>
       </c>
       <c r="J115">
-        <v>40.44</v>
+        <v>0.35</v>
       </c>
       <c r="K115">
-        <v>25.43</v>
+        <v>0.08</v>
       </c>
       <c r="L115">
         <v>1470.54</v>
@@ -11347,7 +11367,7 @@
         <v>15898</v>
       </c>
       <c r="R115">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="S115">
         <v>46.64</v>
@@ -11362,7 +11382,7 @@
         <v>0.86</v>
       </c>
       <c r="W115">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X115">
         <v>0</v>
@@ -11389,7 +11409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:31">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -11418,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="J116">
-        <v>22.26</v>
+        <v>0.16</v>
       </c>
       <c r="K116">
-        <v>21.27</v>
+        <v>0.11</v>
       </c>
       <c r="L116">
         <v>74.69</v>
@@ -11484,7 +11504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:31">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -11513,13 +11533,13 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <v>35.62</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K117">
-        <v>66.81</v>
+        <v>1</v>
       </c>
       <c r="L117">
-        <v>89.29000000000001</v>
+        <v>89.29</v>
       </c>
       <c r="M117">
         <v>665.46</v>
@@ -11558,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z117">
-        <v>0.41</v>
+        <v>0.89</v>
       </c>
       <c r="AA117">
-        <v>89.29000000000001</v>
+        <v>89.29</v>
       </c>
       <c r="AB117">
         <v>665.46</v>
@@ -11579,7 +11599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:31">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -11599,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="G118">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H118">
         <v>0.19</v>
@@ -11608,10 +11628,10 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <v>21.32</v>
+        <v>0.12</v>
       </c>
       <c r="K118">
-        <v>17.98</v>
+        <v>0</v>
       </c>
       <c r="L118">
         <v>125.29</v>
@@ -11644,7 +11664,7 @@
         <v>0</v>
       </c>
       <c r="V118">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="W118">
         <v>0.19</v>
@@ -11674,7 +11694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:31">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -11682,7 +11702,7 @@
         <v>9373</v>
       </c>
       <c r="C119">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="D119">
         <v>25.16</v>
@@ -11697,22 +11717,22 @@
         <v>0.93</v>
       </c>
       <c r="H119">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I119">
         <v>0</v>
       </c>
       <c r="J119">
-        <v>20.69</v>
+        <v>0.15</v>
       </c>
       <c r="K119">
-        <v>17.72</v>
+        <v>0</v>
       </c>
       <c r="L119">
-        <v>92.31999999999999</v>
+        <v>92.32</v>
       </c>
       <c r="M119">
-        <v>1053.09</v>
+        <v>1053.0899999999999</v>
       </c>
       <c r="N119" t="s">
         <v>30</v>
@@ -11727,7 +11747,7 @@
         <v>9373</v>
       </c>
       <c r="R119">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="S119">
         <v>25.16</v>
@@ -11742,7 +11762,7 @@
         <v>0.93</v>
       </c>
       <c r="W119">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X119">
         <v>0</v>
@@ -11754,10 +11774,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>92.31999999999999</v>
+        <v>92.32</v>
       </c>
       <c r="AB119">
-        <v>1053.09</v>
+        <v>1053.0899999999999</v>
       </c>
       <c r="AC119" t="s">
         <v>30</v>
@@ -11769,7 +11789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:31">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -11792,16 +11812,16 @@
         <v>0.86</v>
       </c>
       <c r="H120">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I120">
         <v>0</v>
       </c>
       <c r="J120">
-        <v>20.43</v>
+        <v>0.13</v>
       </c>
       <c r="K120">
-        <v>17.25</v>
+        <v>0</v>
       </c>
       <c r="L120">
         <v>143.93</v>
@@ -11837,7 +11857,7 @@
         <v>0.86</v>
       </c>
       <c r="W120">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X120">
         <v>0</v>
@@ -11864,7 +11884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:31">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -11893,10 +11913,10 @@
         <v>0</v>
       </c>
       <c r="J121">
-        <v>25.89</v>
+        <v>0.26</v>
       </c>
       <c r="K121">
-        <v>21.99</v>
+        <v>0.1</v>
       </c>
       <c r="L121">
         <v>490.14</v>
@@ -11938,10 +11958,10 @@
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Z121">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA121">
         <v>490.14</v>
@@ -11959,7 +11979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:31">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -11988,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="J122">
-        <v>24.23</v>
+        <v>0.22</v>
       </c>
       <c r="K122">
-        <v>19.39</v>
+        <v>0</v>
       </c>
       <c r="L122">
         <v>318.05</v>
@@ -12054,7 +12074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:31">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -12068,13 +12088,13 @@
         <v>51.43</v>
       </c>
       <c r="E123">
-        <v>64.51000000000001</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H123">
         <v>0.06</v>
@@ -12083,10 +12103,10 @@
         <v>0</v>
       </c>
       <c r="J123">
-        <v>26.07</v>
+        <v>0.26</v>
       </c>
       <c r="K123">
-        <v>22.04</v>
+        <v>0.18</v>
       </c>
       <c r="L123">
         <v>264.93</v>
@@ -12113,13 +12133,13 @@
         <v>51.43</v>
       </c>
       <c r="T123">
-        <v>64.51000000000001</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="U123">
         <v>0</v>
       </c>
       <c r="V123">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W123">
         <v>0.06</v>
@@ -12128,7 +12148,7 @@
         <v>0</v>
       </c>
       <c r="Y123">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="Z123">
         <v>0</v>
@@ -12149,7 +12169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:31">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -12178,16 +12198,16 @@
         <v>0</v>
       </c>
       <c r="J124">
-        <v>25.24</v>
+        <v>0.2</v>
       </c>
       <c r="K124">
-        <v>18.88</v>
+        <v>0</v>
       </c>
       <c r="L124">
         <v>282.01</v>
       </c>
       <c r="M124">
-        <v>162.67</v>
+        <v>162.66999999999999</v>
       </c>
       <c r="N124" t="s">
         <v>30</v>
@@ -12232,7 +12252,7 @@
         <v>282.01</v>
       </c>
       <c r="AB124">
-        <v>162.67</v>
+        <v>162.66999999999999</v>
       </c>
       <c r="AC124" t="s">
         <v>30</v>
@@ -12244,7 +12264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:31">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -12273,10 +12293,10 @@
         <v>0</v>
       </c>
       <c r="J125">
-        <v>19.84</v>
+        <v>0</v>
       </c>
       <c r="K125">
-        <v>19.28</v>
+        <v>0</v>
       </c>
       <c r="L125">
         <v>442.59</v>
@@ -12339,7 +12359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:31">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -12368,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="J126">
-        <v>19.28</v>
+        <v>0.03</v>
       </c>
       <c r="K126">
-        <v>18.42</v>
+        <v>0</v>
       </c>
       <c r="L126">
         <v>453.4</v>
@@ -12434,7 +12454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:31">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -12463,7 +12483,7 @@
         <v>0</v>
       </c>
       <c r="J127">
-        <v>19.83</v>
+        <v>0</v>
       </c>
       <c r="K127">
         <v>0</v>
@@ -12529,7 +12549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:31">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -12558,16 +12578,16 @@
         <v>0</v>
       </c>
       <c r="J128">
-        <v>30.07</v>
+        <v>0.42</v>
       </c>
       <c r="K128">
-        <v>20.33</v>
+        <v>0</v>
       </c>
       <c r="L128">
         <v>654.78</v>
       </c>
       <c r="M128">
-        <v>68.31999999999999</v>
+        <v>68.319999999999993</v>
       </c>
       <c r="N128" t="s">
         <v>30</v>
@@ -12612,7 +12632,7 @@
         <v>654.78</v>
       </c>
       <c r="AB128">
-        <v>68.31999999999999</v>
+        <v>68.319999999999993</v>
       </c>
       <c r="AC128" t="s">
         <v>30</v>
@@ -12624,7 +12644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:31">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -12653,10 +12673,10 @@
         <v>0</v>
       </c>
       <c r="J129">
-        <v>21.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K129">
-        <v>19.93</v>
+        <v>0</v>
       </c>
       <c r="L129">
         <v>851.95</v>
@@ -12698,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z129">
         <v>0</v>
@@ -12719,7 +12739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:31">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -12739,7 +12759,7 @@
         <v>0</v>
       </c>
       <c r="G130">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H130">
         <v>0.06</v>
@@ -12748,10 +12768,10 @@
         <v>0</v>
       </c>
       <c r="J130">
-        <v>21.74</v>
+        <v>0.09</v>
       </c>
       <c r="K130">
-        <v>19.08</v>
+        <v>0</v>
       </c>
       <c r="L130">
         <v>833.8</v>
@@ -12784,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="V130">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W130">
         <v>0.06</v>
@@ -12814,7 +12834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:31">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -12843,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="J131">
-        <v>28.06</v>
+        <v>0.3</v>
       </c>
       <c r="K131">
-        <v>20.44</v>
+        <v>0.01</v>
       </c>
       <c r="L131">
         <v>853.26</v>
@@ -12909,7 +12929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:31">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -12938,16 +12958,16 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <v>20.94</v>
+        <v>0.05</v>
       </c>
       <c r="K132">
-        <v>22.31</v>
+        <v>0.06</v>
       </c>
       <c r="L132">
         <v>906.42</v>
       </c>
       <c r="M132">
-        <v>546.42</v>
+        <v>546.41999999999996</v>
       </c>
       <c r="N132" t="s">
         <v>30</v>
@@ -12992,7 +13012,7 @@
         <v>906.42</v>
       </c>
       <c r="AB132">
-        <v>546.42</v>
+        <v>546.41999999999996</v>
       </c>
       <c r="AC132" t="s">
         <v>30</v>
@@ -13004,7 +13024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:31">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -13033,10 +13053,10 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <v>20.78</v>
+        <v>0.06</v>
       </c>
       <c r="K133">
-        <v>19.82</v>
+        <v>0</v>
       </c>
       <c r="L133">
         <v>1157.58</v>
@@ -13099,7 +13119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:31">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -13128,13 +13148,13 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <v>22.24</v>
+        <v>0.09</v>
       </c>
       <c r="K134">
-        <v>20.91</v>
+        <v>0</v>
       </c>
       <c r="L134">
-        <v>1095.63</v>
+        <v>1095.6300000000001</v>
       </c>
       <c r="M134">
         <v>133.62</v>
@@ -13179,7 +13199,7 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>1095.63</v>
+        <v>1095.6300000000001</v>
       </c>
       <c r="AB134">
         <v>133.62</v>
@@ -13194,7 +13214,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:31">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -13223,10 +13243,10 @@
         <v>0</v>
       </c>
       <c r="J135">
-        <v>23.56</v>
+        <v>0.18</v>
       </c>
       <c r="K135">
-        <v>20.17</v>
+        <v>0.01</v>
       </c>
       <c r="L135">
         <v>1311.86</v>
@@ -13289,7 +13309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:31">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -13303,7 +13323,7 @@
         <v>46.48</v>
       </c>
       <c r="E136">
-        <v>33.73</v>
+        <v>33.729999999999997</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -13318,10 +13338,10 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>21.06</v>
+        <v>0.06</v>
       </c>
       <c r="K136">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="L136">
         <v>1148.75</v>
@@ -13348,7 +13368,7 @@
         <v>46.48</v>
       </c>
       <c r="T136">
-        <v>33.73</v>
+        <v>33.729999999999997</v>
       </c>
       <c r="U136">
         <v>0</v>
@@ -13384,7 +13404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:31">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -13413,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>20.64</v>
+        <v>0.01</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -13479,7 +13499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:31">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -13508,10 +13528,10 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>19.18</v>
+        <v>0.03</v>
       </c>
       <c r="K138">
-        <v>17.93</v>
+        <v>0</v>
       </c>
       <c r="L138">
         <v>1204.24</v>
@@ -13574,7 +13594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:31">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -13603,10 +13623,10 @@
         <v>0</v>
       </c>
       <c r="J139">
-        <v>21.06</v>
+        <v>0.08</v>
       </c>
       <c r="K139">
-        <v>18.98</v>
+        <v>0</v>
       </c>
       <c r="L139">
         <v>1417.04</v>
@@ -13669,7 +13689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:31">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -13698,10 +13718,10 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <v>23.71</v>
+        <v>0.22</v>
       </c>
       <c r="K140">
-        <v>18.4</v>
+        <v>0.01</v>
       </c>
       <c r="L140">
         <v>1364.62</v>
@@ -13764,7 +13784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:31">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -13793,10 +13813,10 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <v>26.37</v>
+        <v>0.34</v>
       </c>
       <c r="K141">
-        <v>21.39</v>
+        <v>0.09</v>
       </c>
       <c r="L141">
         <v>1475.48</v>
@@ -13859,7 +13879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:31">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -13888,10 +13908,10 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>24.54</v>
+        <v>0.26</v>
       </c>
       <c r="K142">
-        <v>20.75</v>
+        <v>0.05</v>
       </c>
       <c r="L142">
         <v>1528.05</v>
@@ -13954,7 +13974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143" spans="1:31">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -13983,10 +14003,10 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <v>23.7</v>
+        <v>0.22</v>
       </c>
       <c r="K143">
-        <v>18.83</v>
+        <v>0</v>
       </c>
       <c r="L143">
         <v>1525.53</v>
@@ -14049,7 +14069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:31">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -14078,10 +14098,10 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <v>21.21</v>
+        <v>0.1</v>
       </c>
       <c r="K144">
-        <v>41.56</v>
+        <v>0.59</v>
       </c>
       <c r="L144">
         <v>1536.72</v>
@@ -14144,7 +14164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:31">
+    <row r="145" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -14155,7 +14175,7 @@
         <v>2.44</v>
       </c>
       <c r="D145">
-        <v>86.79000000000001</v>
+        <v>86.79</v>
       </c>
       <c r="E145">
         <v>86.67</v>
@@ -14164,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="G145">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H145">
         <v>0.71</v>
@@ -14173,10 +14193,10 @@
         <v>0</v>
       </c>
       <c r="J145">
-        <v>22.84</v>
+        <v>0.12</v>
       </c>
       <c r="K145">
-        <v>27.41</v>
+        <v>0.24</v>
       </c>
       <c r="L145">
         <v>486.4</v>
@@ -14200,7 +14220,7 @@
         <v>2.44</v>
       </c>
       <c r="S145">
-        <v>86.79000000000001</v>
+        <v>86.79</v>
       </c>
       <c r="T145">
         <v>86.67</v>
@@ -14209,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="V145">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W145">
         <v>0.71</v>
@@ -14218,10 +14238,10 @@
         <v>0</v>
       </c>
       <c r="Y145">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="Z145">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="AA145">
         <v>486.4</v>
@@ -14239,7 +14259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:31">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -14268,10 +14288,10 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <v>25</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K146">
-        <v>19.39</v>
+        <v>0.05</v>
       </c>
       <c r="L146">
         <v>50.4</v>
@@ -14313,10 +14333,10 @@
         <v>0</v>
       </c>
       <c r="Y146">
+        <v>0.04</v>
+      </c>
+      <c r="Z146">
         <v>0.02</v>
-      </c>
-      <c r="Z146">
-        <v>0.01</v>
       </c>
       <c r="AA146">
         <v>50.4</v>
@@ -14334,7 +14354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:31">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -14363,10 +14383,10 @@
         <v>0</v>
       </c>
       <c r="J147">
-        <v>19.22</v>
+        <v>0.02</v>
       </c>
       <c r="K147">
-        <v>21.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L147">
         <v>271.75</v>
@@ -14408,10 +14428,10 @@
         <v>0</v>
       </c>
       <c r="Y147">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z147">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="AA147">
         <v>271.75</v>
@@ -14429,7 +14449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:31">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -14458,10 +14478,10 @@
         <v>0</v>
       </c>
       <c r="J148">
-        <v>26.3</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K148">
-        <v>29.16</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L148">
         <v>655.85</v>
@@ -14503,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="Y148">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="Z148">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="AA148">
         <v>655.85</v>
@@ -14524,7 +14544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:31">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -14553,13 +14573,13 @@
         <v>0</v>
       </c>
       <c r="J149">
-        <v>20.08</v>
+        <v>0.03</v>
       </c>
       <c r="K149">
-        <v>31.26</v>
+        <v>0.25</v>
       </c>
       <c r="L149">
-        <v>533.5599999999999</v>
+        <v>533.55999999999995</v>
       </c>
       <c r="M149">
         <v>661.42</v>
@@ -14598,13 +14618,13 @@
         <v>0</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z149">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="AA149">
-        <v>533.5599999999999</v>
+        <v>533.55999999999995</v>
       </c>
       <c r="AB149">
         <v>661.42</v>
@@ -14619,7 +14639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:31">
+    <row r="150" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -14642,16 +14662,16 @@
         <v>0.31</v>
       </c>
       <c r="H150">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I150">
         <v>0</v>
       </c>
       <c r="J150">
-        <v>31.38</v>
+        <v>0.34</v>
       </c>
       <c r="K150">
-        <v>41.68</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L150">
         <v>550.02</v>
@@ -14687,16 +14707,16 @@
         <v>0.31</v>
       </c>
       <c r="W150">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X150">
         <v>0</v>
       </c>
       <c r="Y150">
-        <v>0.17</v>
+        <v>0.39</v>
       </c>
       <c r="Z150">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="AA150">
         <v>550.02</v>
@@ -14714,7 +14734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:31">
+    <row r="151" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -14746,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>36.79</v>
+        <v>0.42</v>
       </c>
       <c r="L151">
         <v>708.35</v>
@@ -14791,7 +14811,7 @@
         <v>0</v>
       </c>
       <c r="Z151">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="AA151">
         <v>708.35</v>
@@ -14809,7 +14829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:31">
+    <row r="152" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -14838,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="J152">
-        <v>24.33</v>
+        <v>0.17</v>
       </c>
       <c r="K152">
-        <v>26.56</v>
+        <v>0.2</v>
       </c>
       <c r="L152">
         <v>832.67</v>
@@ -14883,10 +14903,10 @@
         <v>0</v>
       </c>
       <c r="Y152">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="Z152">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="AA152">
         <v>832.67</v>
@@ -14904,7 +14924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:31">
+    <row r="153" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -14933,16 +14953,16 @@
         <v>0</v>
       </c>
       <c r="J153">
-        <v>21.15</v>
+        <v>0.01</v>
       </c>
       <c r="K153">
-        <v>37.39</v>
+        <v>0.26</v>
       </c>
       <c r="L153">
         <v>935.74</v>
       </c>
       <c r="M153">
-        <v>264.9</v>
+        <v>264.89999999999998</v>
       </c>
       <c r="N153" t="s">
         <v>30</v>
@@ -14981,13 +15001,13 @@
         <v>0</v>
       </c>
       <c r="Z153">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA153">
         <v>935.74</v>
       </c>
       <c r="AB153">
-        <v>264.9</v>
+        <v>264.89999999999998</v>
       </c>
       <c r="AC153" t="s">
         <v>30</v>
@@ -14999,7 +15019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:31">
+    <row r="154" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -15019,7 +15039,7 @@
         <v>0</v>
       </c>
       <c r="G154">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H154">
         <v>0.71</v>
@@ -15028,10 +15048,10 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <v>20.69</v>
+        <v>0.02</v>
       </c>
       <c r="K154">
-        <v>26.61</v>
+        <v>0.16</v>
       </c>
       <c r="L154">
         <v>1292.79</v>
@@ -15064,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="V154">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W154">
         <v>0.71</v>
@@ -15076,7 +15096,7 @@
         <v>0</v>
       </c>
       <c r="Z154">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="AA154">
         <v>1292.79</v>
@@ -15094,7 +15114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:31">
+    <row r="155" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -15114,7 +15134,7 @@
         <v>0</v>
       </c>
       <c r="G155">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H155">
         <v>0.71</v>
@@ -15123,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="J155">
-        <v>19.98</v>
+        <v>0.05</v>
       </c>
       <c r="K155">
-        <v>30.34</v>
+        <v>0.31</v>
       </c>
       <c r="L155">
         <v>1116.52</v>
@@ -15159,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="V155">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W155">
         <v>0.71</v>
@@ -15168,10 +15188,10 @@
         <v>0</v>
       </c>
       <c r="Y155">
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Z155">
-        <v>0.23</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA155">
         <v>1116.52</v>
@@ -15189,7 +15209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:31">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -15218,10 +15238,10 @@
         <v>0</v>
       </c>
       <c r="J156">
-        <v>23.56</v>
+        <v>0.13</v>
       </c>
       <c r="K156">
-        <v>30.14</v>
+        <v>0.27</v>
       </c>
       <c r="L156">
         <v>1291.58</v>
@@ -15263,10 +15283,10 @@
         <v>0</v>
       </c>
       <c r="Y156">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="Z156">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="AA156">
         <v>1291.58</v>
@@ -15284,7 +15304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:31">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -15295,7 +15315,7 @@
         <v>2.64</v>
       </c>
       <c r="D157">
-        <v>67.76000000000001</v>
+        <v>67.760000000000005</v>
       </c>
       <c r="E157">
         <v>118.18</v>
@@ -15313,10 +15333,10 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>21.99</v>
+        <v>0.1</v>
       </c>
       <c r="K157">
-        <v>23.38</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L157">
         <v>1418.48</v>
@@ -15340,7 +15360,7 @@
         <v>2.64</v>
       </c>
       <c r="S157">
-        <v>67.76000000000001</v>
+        <v>67.760000000000005</v>
       </c>
       <c r="T157">
         <v>118.18</v>
@@ -15361,7 +15381,7 @@
         <v>0</v>
       </c>
       <c r="Z157">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="AA157">
         <v>1418.48</v>
@@ -15379,7 +15399,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:31">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -15390,7 +15410,7 @@
         <v>1.06</v>
       </c>
       <c r="D158">
-        <v>40.16</v>
+        <v>40.159999999999997</v>
       </c>
       <c r="E158">
         <v>95.12</v>
@@ -15408,10 +15428,10 @@
         <v>0</v>
       </c>
       <c r="J158">
-        <v>42.73</v>
+        <v>0.61</v>
       </c>
       <c r="K158">
-        <v>22.05</v>
+        <v>0.1</v>
       </c>
       <c r="L158">
         <v>1479.43</v>
@@ -15435,7 +15455,7 @@
         <v>1.06</v>
       </c>
       <c r="S158">
-        <v>40.16</v>
+        <v>40.159999999999997</v>
       </c>
       <c r="T158">
         <v>95.12</v>
@@ -15453,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="Y158">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="Z158">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AA158">
         <v>1479.43</v>
@@ -15474,7 +15494,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:31">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -15485,7 +15505,7 @@
         <v>1.64</v>
       </c>
       <c r="D159">
-        <v>81.26000000000001</v>
+        <v>81.260000000000005</v>
       </c>
       <c r="E159">
         <v>67.66</v>
@@ -15503,16 +15523,16 @@
         <v>0</v>
       </c>
       <c r="J159">
-        <v>21.79</v>
+        <v>0.13</v>
       </c>
       <c r="K159">
-        <v>26.95</v>
+        <v>0.22</v>
       </c>
       <c r="L159">
         <v>1479.19</v>
       </c>
       <c r="M159">
-        <v>674.3099999999999</v>
+        <v>674.31</v>
       </c>
       <c r="N159" t="s">
         <v>30</v>
@@ -15530,7 +15550,7 @@
         <v>1.64</v>
       </c>
       <c r="S159">
-        <v>81.26000000000001</v>
+        <v>81.260000000000005</v>
       </c>
       <c r="T159">
         <v>67.66</v>
@@ -15548,16 +15568,16 @@
         <v>0</v>
       </c>
       <c r="Y159">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="Z159">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="AA159">
         <v>1479.19</v>
       </c>
       <c r="AB159">
-        <v>674.3099999999999</v>
+        <v>674.31</v>
       </c>
       <c r="AC159" t="s">
         <v>30</v>
@@ -15569,7 +15589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:31">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -15598,10 +15618,10 @@
         <v>0</v>
       </c>
       <c r="J160">
-        <v>20.25</v>
+        <v>0.08</v>
       </c>
       <c r="K160">
-        <v>21.72</v>
+        <v>0.16</v>
       </c>
       <c r="L160">
         <v>175.55</v>
@@ -15643,10 +15663,10 @@
         <v>0</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z160">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="AA160">
         <v>175.55</v>
@@ -15664,7 +15684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:31">
+    <row r="161" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -15693,13 +15713,13 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>22.59</v>
+        <v>0.12</v>
       </c>
       <c r="K161">
-        <v>26.09</v>
+        <v>0.18</v>
       </c>
       <c r="L161">
-        <v>160.8</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="M161">
         <v>483.63</v>
@@ -15738,13 +15758,13 @@
         <v>0</v>
       </c>
       <c r="Y161">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="Z161">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="AA161">
-        <v>160.8</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="AB161">
         <v>483.63</v>
@@ -15759,7 +15779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:31">
+    <row r="162" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -15773,7 +15793,7 @@
         <v>47.55</v>
       </c>
       <c r="E162">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -15782,22 +15802,22 @@
         <v>0.31</v>
       </c>
       <c r="H162">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I162">
         <v>0</v>
       </c>
       <c r="J162">
-        <v>19.83</v>
+        <v>0.05</v>
       </c>
       <c r="K162">
-        <v>34.62</v>
+        <v>0.31</v>
       </c>
       <c r="L162">
         <v>205.29</v>
       </c>
       <c r="M162">
-        <v>913.5700000000001</v>
+        <v>913.57</v>
       </c>
       <c r="N162" t="s">
         <v>30</v>
@@ -15818,7 +15838,7 @@
         <v>47.55</v>
       </c>
       <c r="T162">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="U162">
         <v>0</v>
@@ -15827,22 +15847,22 @@
         <v>0.31</v>
       </c>
       <c r="W162">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X162">
         <v>0</v>
       </c>
       <c r="Y162">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z162">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="AA162">
         <v>205.29</v>
       </c>
       <c r="AB162">
-        <v>913.5700000000001</v>
+        <v>913.57</v>
       </c>
       <c r="AC162" t="s">
         <v>30</v>
@@ -15854,7 +15874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:31">
+    <row r="163" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -15883,10 +15903,10 @@
         <v>0</v>
       </c>
       <c r="J163">
-        <v>32.81</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K163">
-        <v>34.69</v>
+        <v>0.48</v>
       </c>
       <c r="L163">
         <v>42.2</v>
@@ -15928,10 +15948,10 @@
         <v>0</v>
       </c>
       <c r="Y163">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="Z163">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="AA163">
         <v>42.2</v>
@@ -15949,7 +15969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:31">
+    <row r="164" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -15963,7 +15983,7 @@
         <v>62.06</v>
       </c>
       <c r="E164">
-        <v>91.15000000000001</v>
+        <v>91.15</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -15978,10 +15998,10 @@
         <v>0</v>
       </c>
       <c r="J164">
-        <v>21.87</v>
+        <v>0.1</v>
       </c>
       <c r="K164">
-        <v>29.44</v>
+        <v>0.25</v>
       </c>
       <c r="L164">
         <v>404.03</v>
@@ -16008,7 +16028,7 @@
         <v>62.06</v>
       </c>
       <c r="T164">
-        <v>91.15000000000001</v>
+        <v>91.15</v>
       </c>
       <c r="U164">
         <v>0</v>
@@ -16023,10 +16043,10 @@
         <v>0</v>
       </c>
       <c r="Y164">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="Z164">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="AA164">
         <v>404.03</v>
@@ -16044,7 +16064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:31">
+    <row r="165" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -16073,10 +16093,10 @@
         <v>0</v>
       </c>
       <c r="J165">
-        <v>25.55</v>
+        <v>0.17</v>
       </c>
       <c r="K165">
-        <v>44.83</v>
+        <v>0.46</v>
       </c>
       <c r="L165">
         <v>471.35</v>
@@ -16118,10 +16138,10 @@
         <v>0</v>
       </c>
       <c r="Y165">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="Z165">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="AA165">
         <v>471.35</v>
@@ -16139,7 +16159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:31">
+    <row r="166" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -16168,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>21.91</v>
+        <v>0.05</v>
       </c>
       <c r="K166">
-        <v>28.49</v>
+        <v>0.21</v>
       </c>
       <c r="L166">
         <v>615.87</v>
@@ -16213,10 +16233,10 @@
         <v>0</v>
       </c>
       <c r="Y166">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="Z166">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="AA166">
         <v>615.87</v>
@@ -16234,7 +16254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:31">
+    <row r="167" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -16263,10 +16283,10 @@
         <v>0</v>
       </c>
       <c r="J167">
-        <v>23.09</v>
+        <v>0.15</v>
       </c>
       <c r="K167">
-        <v>22.22</v>
+        <v>0.11</v>
       </c>
       <c r="L167">
         <v>689.09</v>
@@ -16308,10 +16328,10 @@
         <v>0</v>
       </c>
       <c r="Y167">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z167">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AA167">
         <v>689.09</v>
@@ -16329,7 +16349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:31">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -16337,7 +16357,7 @@
         <v>9351</v>
       </c>
       <c r="C168">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="D168">
         <v>55.11</v>
@@ -16349,7 +16369,7 @@
         <v>0</v>
       </c>
       <c r="G168">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="H168">
         <v>0.31</v>
@@ -16358,10 +16378,10 @@
         <v>0</v>
       </c>
       <c r="J168">
-        <v>21.62</v>
+        <v>0.05</v>
       </c>
       <c r="K168">
-        <v>21.43</v>
+        <v>0.02</v>
       </c>
       <c r="L168">
         <v>509.96</v>
@@ -16382,7 +16402,7 @@
         <v>9351</v>
       </c>
       <c r="R168">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="S168">
         <v>55.11</v>
@@ -16394,7 +16414,7 @@
         <v>0</v>
       </c>
       <c r="V168">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="W168">
         <v>0.31</v>
@@ -16406,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="Z168">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AA168">
         <v>509.96</v>
@@ -16424,7 +16444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:31">
+    <row r="169" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -16453,10 +16473,10 @@
         <v>0</v>
       </c>
       <c r="J169">
-        <v>27.79</v>
+        <v>0.25</v>
       </c>
       <c r="K169">
-        <v>26.09</v>
+        <v>0.32</v>
       </c>
       <c r="L169">
         <v>944.33</v>
@@ -16498,10 +16518,10 @@
         <v>0</v>
       </c>
       <c r="Y169">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="Z169">
-        <v>0.22</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA169">
         <v>944.33</v>
@@ -16519,7 +16539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:31">
+    <row r="170" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -16530,7 +16550,7 @@
         <v>3</v>
       </c>
       <c r="D170">
-        <v>75.26000000000001</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="E170">
         <v>62.85</v>
@@ -16548,10 +16568,10 @@
         <v>0</v>
       </c>
       <c r="J170">
-        <v>24.2</v>
+        <v>0.1</v>
       </c>
       <c r="K170">
-        <v>24.62</v>
+        <v>0.15</v>
       </c>
       <c r="L170">
         <v>864.24</v>
@@ -16575,7 +16595,7 @@
         <v>3</v>
       </c>
       <c r="S170">
-        <v>75.26000000000001</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="T170">
         <v>62.85</v>
@@ -16593,10 +16613,10 @@
         <v>0</v>
       </c>
       <c r="Y170">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="Z170">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="AA170">
         <v>864.24</v>
@@ -16614,7 +16634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:31">
+    <row r="171" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -16625,7 +16645,7 @@
         <v>1.71</v>
       </c>
       <c r="D171">
-        <v>78.84999999999999</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="E171">
         <v>85.16</v>
@@ -16634,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="G171">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H171">
         <v>0.72</v>
@@ -16643,10 +16663,10 @@
         <v>0</v>
       </c>
       <c r="J171">
-        <v>24.22</v>
+        <v>0.22</v>
       </c>
       <c r="K171">
-        <v>29.09</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L171">
         <v>1187.75</v>
@@ -16670,7 +16690,7 @@
         <v>1.71</v>
       </c>
       <c r="S171">
-        <v>78.84999999999999</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="T171">
         <v>85.16</v>
@@ -16679,7 +16699,7 @@
         <v>0</v>
       </c>
       <c r="V171">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W171">
         <v>0.72</v>
@@ -16688,10 +16708,10 @@
         <v>0</v>
       </c>
       <c r="Y171">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="Z171">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="AA171">
         <v>1187.75</v>
@@ -16709,7 +16729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:31">
+    <row r="172" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -16732,16 +16752,16 @@
         <v>0.42</v>
       </c>
       <c r="H172">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I172">
         <v>0</v>
       </c>
       <c r="J172">
-        <v>27.29</v>
+        <v>0.27</v>
       </c>
       <c r="K172">
-        <v>32.35</v>
+        <v>0.3</v>
       </c>
       <c r="L172">
         <v>1156.94</v>
@@ -16777,16 +16797,16 @@
         <v>0.42</v>
       </c>
       <c r="W172">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X172">
         <v>0</v>
       </c>
       <c r="Y172">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="Z172">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="AA172">
         <v>1156.94</v>
@@ -16804,7 +16824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:31">
+    <row r="173" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -16815,7 +16835,7 @@
         <v>3.32</v>
       </c>
       <c r="D173">
-        <v>68.93000000000001</v>
+        <v>68.930000000000007</v>
       </c>
       <c r="E173">
         <v>49.92</v>
@@ -16833,10 +16853,10 @@
         <v>0</v>
       </c>
       <c r="J173">
-        <v>23.26</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K173">
-        <v>23.09</v>
+        <v>0.12</v>
       </c>
       <c r="L173">
         <v>1393.82</v>
@@ -16860,7 +16880,7 @@
         <v>3.32</v>
       </c>
       <c r="S173">
-        <v>68.93000000000001</v>
+        <v>68.930000000000007</v>
       </c>
       <c r="T173">
         <v>49.92</v>
@@ -16878,10 +16898,10 @@
         <v>0</v>
       </c>
       <c r="Y173">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z173">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="AA173">
         <v>1393.82</v>
@@ -16899,7 +16919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:31">
+    <row r="174" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -16928,10 +16948,10 @@
         <v>0</v>
       </c>
       <c r="J174">
-        <v>28.95</v>
+        <v>0.37</v>
       </c>
       <c r="K174">
-        <v>31.64</v>
+        <v>0.3</v>
       </c>
       <c r="L174">
         <v>1496.99</v>
@@ -16973,10 +16993,10 @@
         <v>0</v>
       </c>
       <c r="Y174">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Z174">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="AA174">
         <v>1496.99</v>
@@ -16994,7 +17014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:31">
+    <row r="175" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -17005,10 +17025,10 @@
         <v>2.27</v>
       </c>
       <c r="D175">
-        <v>33.59</v>
+        <v>33.590000000000003</v>
       </c>
       <c r="E175">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -17023,10 +17043,10 @@
         <v>0</v>
       </c>
       <c r="J175">
-        <v>25.32</v>
+        <v>0.26</v>
       </c>
       <c r="K175">
-        <v>18.64</v>
+        <v>0</v>
       </c>
       <c r="L175">
         <v>1528</v>
@@ -17050,10 +17070,10 @@
         <v>2.27</v>
       </c>
       <c r="S175">
-        <v>33.59</v>
+        <v>33.590000000000003</v>
       </c>
       <c r="T175">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="U175">
         <v>0</v>
@@ -17089,7 +17109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:31">
+    <row r="176" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -17112,22 +17132,22 @@
         <v>0.31</v>
       </c>
       <c r="H176">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I176">
         <v>0</v>
       </c>
       <c r="J176">
-        <v>19.18</v>
+        <v>0.05</v>
       </c>
       <c r="K176">
-        <v>25.35</v>
+        <v>0.2</v>
       </c>
       <c r="L176">
         <v>168.22</v>
       </c>
       <c r="M176">
-        <v>137.05</v>
+        <v>137.05000000000001</v>
       </c>
       <c r="N176" t="s">
         <v>30</v>
@@ -17157,7 +17177,7 @@
         <v>0.31</v>
       </c>
       <c r="W176">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X176">
         <v>0</v>
@@ -17166,13 +17186,13 @@
         <v>0</v>
       </c>
       <c r="Z176">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="AA176">
         <v>168.22</v>
       </c>
       <c r="AB176">
-        <v>137.05</v>
+        <v>137.05000000000001</v>
       </c>
       <c r="AC176" t="s">
         <v>30</v>
@@ -17184,7 +17204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:31">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -17213,10 +17233,10 @@
         <v>0</v>
       </c>
       <c r="J177">
-        <v>22.79</v>
+        <v>0.06</v>
       </c>
       <c r="K177">
-        <v>30.69</v>
+        <v>0.17</v>
       </c>
       <c r="L177">
         <v>336.78</v>
@@ -17258,10 +17278,10 @@
         <v>0</v>
       </c>
       <c r="Y177">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="Z177">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="AA177">
         <v>336.78</v>
@@ -17279,7 +17299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:31">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -17308,10 +17328,10 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>25.05</v>
+        <v>0.19</v>
       </c>
       <c r="K178">
-        <v>23.99</v>
+        <v>0.2</v>
       </c>
       <c r="L178">
         <v>105.62</v>
@@ -17353,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="Y178">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z178">
         <v>0.01</v>
@@ -17374,7 +17394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:31">
+    <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -17403,10 +17423,10 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>21.79</v>
+        <v>0.15</v>
       </c>
       <c r="K179">
-        <v>20.49</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L179">
         <v>218.24</v>
@@ -17448,10 +17468,10 @@
         <v>0</v>
       </c>
       <c r="Y179">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Z179">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AA179">
         <v>218.24</v>
@@ -17469,7 +17489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:31">
+    <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -17498,16 +17518,16 @@
         <v>0</v>
       </c>
       <c r="J180">
-        <v>22.37</v>
+        <v>0.15</v>
       </c>
       <c r="K180">
-        <v>26.52</v>
+        <v>0.18</v>
       </c>
       <c r="L180">
         <v>501.58</v>
       </c>
       <c r="M180">
-        <v>994.4299999999999</v>
+        <v>994.43</v>
       </c>
       <c r="N180" t="s">
         <v>30</v>
@@ -17546,13 +17566,13 @@
         <v>0.01</v>
       </c>
       <c r="Z180">
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA180">
         <v>501.58</v>
       </c>
       <c r="AB180">
-        <v>994.4299999999999</v>
+        <v>994.43</v>
       </c>
       <c r="AC180" t="s">
         <v>30</v>
@@ -17564,7 +17584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:31">
+    <row r="181" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -17593,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="J181">
-        <v>29.3</v>
+        <v>0.32</v>
       </c>
       <c r="K181">
-        <v>22.09</v>
+        <v>0.15</v>
       </c>
       <c r="L181">
         <v>275.51</v>
@@ -17659,7 +17679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:31">
+    <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -17688,10 +17708,10 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>24.43</v>
+        <v>0.22</v>
       </c>
       <c r="K182">
-        <v>39.89</v>
+        <v>0.43</v>
       </c>
       <c r="L182">
         <v>771.37</v>
@@ -17733,10 +17753,10 @@
         <v>0</v>
       </c>
       <c r="Y182">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="Z182">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA182">
         <v>771.37</v>
@@ -17754,7 +17774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:31">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -17768,7 +17788,7 @@
         <v>63.81</v>
       </c>
       <c r="E183">
-        <v>83.09999999999999</v>
+        <v>83.1</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -17783,16 +17803,16 @@
         <v>0</v>
       </c>
       <c r="J183">
-        <v>22.25</v>
+        <v>0.08</v>
       </c>
       <c r="K183">
-        <v>31.82</v>
+        <v>0.27</v>
       </c>
       <c r="L183">
-        <v>809.5599999999999</v>
+        <v>809.56</v>
       </c>
       <c r="M183">
-        <v>619.1900000000001</v>
+        <v>619.19000000000005</v>
       </c>
       <c r="N183" t="s">
         <v>30</v>
@@ -17813,7 +17833,7 @@
         <v>63.81</v>
       </c>
       <c r="T183">
-        <v>83.09999999999999</v>
+        <v>83.1</v>
       </c>
       <c r="U183">
         <v>0</v>
@@ -17828,16 +17848,16 @@
         <v>0</v>
       </c>
       <c r="Y183">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="Z183">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="AA183">
-        <v>809.5599999999999</v>
+        <v>809.56</v>
       </c>
       <c r="AB183">
-        <v>619.1900000000001</v>
+        <v>619.19000000000005</v>
       </c>
       <c r="AC183" t="s">
         <v>30</v>
@@ -17849,7 +17869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:31">
+    <row r="184" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -17860,10 +17880,10 @@
         <v>6.83</v>
       </c>
       <c r="D184">
-        <v>66.26000000000001</v>
+        <v>66.260000000000005</v>
       </c>
       <c r="E184">
-        <v>95.29000000000001</v>
+        <v>95.29</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -17872,22 +17892,22 @@
         <v>0.43</v>
       </c>
       <c r="H184">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I184">
         <v>0</v>
       </c>
       <c r="J184">
-        <v>25.37</v>
+        <v>0.25</v>
       </c>
       <c r="K184">
-        <v>39.91</v>
+        <v>0.39</v>
       </c>
       <c r="L184">
-        <v>1076.4</v>
+        <v>1076.4000000000001</v>
       </c>
       <c r="M184">
-        <v>82.73999999999999</v>
+        <v>82.74</v>
       </c>
       <c r="N184" t="s">
         <v>30</v>
@@ -17905,10 +17925,10 @@
         <v>6.83</v>
       </c>
       <c r="S184">
-        <v>66.26000000000001</v>
+        <v>66.260000000000005</v>
       </c>
       <c r="T184">
-        <v>95.29000000000001</v>
+        <v>95.29</v>
       </c>
       <c r="U184">
         <v>0</v>
@@ -17917,22 +17937,22 @@
         <v>0.43</v>
       </c>
       <c r="W184">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="X184">
         <v>0</v>
       </c>
       <c r="Y184">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="Z184">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="AA184">
-        <v>1076.4</v>
+        <v>1076.4000000000001</v>
       </c>
       <c r="AB184">
-        <v>82.73999999999999</v>
+        <v>82.74</v>
       </c>
       <c r="AC184" t="s">
         <v>30</v>
@@ -17944,7 +17964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:31">
+    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -17967,22 +17987,22 @@
         <v>0.19</v>
       </c>
       <c r="H185">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I185">
         <v>0</v>
       </c>
       <c r="J185">
-        <v>25.26</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K185">
-        <v>24.83</v>
+        <v>0.16</v>
       </c>
       <c r="L185">
-        <v>788.6799999999999</v>
+        <v>788.68</v>
       </c>
       <c r="M185">
-        <v>935.6900000000001</v>
+        <v>935.69</v>
       </c>
       <c r="N185" t="s">
         <v>30</v>
@@ -18012,22 +18032,22 @@
         <v>0.19</v>
       </c>
       <c r="W185">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X185">
         <v>0</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z185">
-        <v>0.12</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA185">
-        <v>788.6799999999999</v>
+        <v>788.68</v>
       </c>
       <c r="AB185">
-        <v>935.6900000000001</v>
+        <v>935.69</v>
       </c>
       <c r="AC185" t="s">
         <v>30</v>
@@ -18039,7 +18059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:31">
+    <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -18068,10 +18088,10 @@
         <v>0</v>
       </c>
       <c r="J186">
-        <v>23.6</v>
+        <v>0.12</v>
       </c>
       <c r="K186">
-        <v>30.48</v>
+        <v>0.23</v>
       </c>
       <c r="L186">
         <v>1162.53</v>
@@ -18113,10 +18133,10 @@
         <v>0</v>
       </c>
       <c r="Y186">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="Z186">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="AA186">
         <v>1162.53</v>
@@ -18134,7 +18154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:31">
+    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -18157,22 +18177,22 @@
         <v>0.31</v>
       </c>
       <c r="H187">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I187">
         <v>0</v>
       </c>
       <c r="J187">
-        <v>20.27</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K187">
-        <v>31.26</v>
+        <v>0.2</v>
       </c>
       <c r="L187">
         <v>1096.44</v>
       </c>
       <c r="M187">
-        <v>1028.89</v>
+        <v>1028.8900000000001</v>
       </c>
       <c r="N187" t="s">
         <v>30</v>
@@ -18202,22 +18222,22 @@
         <v>0.31</v>
       </c>
       <c r="W187">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X187">
         <v>0</v>
       </c>
       <c r="Y187">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="Z187">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="AA187">
         <v>1096.44</v>
       </c>
       <c r="AB187">
-        <v>1028.89</v>
+        <v>1028.8900000000001</v>
       </c>
       <c r="AC187" t="s">
         <v>30</v>
@@ -18229,7 +18249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:31">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -18258,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="J188">
-        <v>20.62</v>
+        <v>0.08</v>
       </c>
       <c r="K188">
-        <v>39.04</v>
+        <v>0.4</v>
       </c>
       <c r="L188">
         <v>1345.22</v>
@@ -18306,7 +18326,7 @@
         <v>0</v>
       </c>
       <c r="Z188">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="AA188">
         <v>1345.22</v>
@@ -18324,7 +18344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:31">
+    <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -18338,7 +18358,7 @@
         <v>76.48</v>
       </c>
       <c r="E189">
-        <v>94.65000000000001</v>
+        <v>94.65</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -18353,10 +18373,10 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>24.44</v>
+        <v>0.19</v>
       </c>
       <c r="K189">
-        <v>23.44</v>
+        <v>0.15</v>
       </c>
       <c r="L189">
         <v>1348.5</v>
@@ -18383,7 +18403,7 @@
         <v>76.48</v>
       </c>
       <c r="T189">
-        <v>94.65000000000001</v>
+        <v>94.65</v>
       </c>
       <c r="U189">
         <v>0</v>
@@ -18398,10 +18418,10 @@
         <v>0</v>
       </c>
       <c r="Y189">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="Z189">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="AA189">
         <v>1348.5</v>
@@ -18419,7 +18439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="190" spans="1:31">
+    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -18430,10 +18450,10 @@
         <v>1.21</v>
       </c>
       <c r="D190">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="E190">
-        <v>79.65000000000001</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -18448,10 +18468,10 @@
         <v>0</v>
       </c>
       <c r="J190">
-        <v>21.04</v>
+        <v>0.03</v>
       </c>
       <c r="K190">
-        <v>32.84</v>
+        <v>0.36</v>
       </c>
       <c r="L190">
         <v>1442.74</v>
@@ -18475,10 +18495,10 @@
         <v>1.21</v>
       </c>
       <c r="S190">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="T190">
-        <v>79.65000000000001</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="U190">
         <v>0</v>
@@ -18493,10 +18513,10 @@
         <v>0</v>
       </c>
       <c r="Y190">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Z190">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="AA190">
         <v>1442.74</v>
@@ -18514,7 +18534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:31">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -18537,22 +18557,22 @@
         <v>0.72</v>
       </c>
       <c r="H191">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I191">
         <v>0</v>
       </c>
       <c r="J191">
-        <v>27.43</v>
+        <v>0.5</v>
       </c>
       <c r="K191">
-        <v>23.58</v>
+        <v>0.26</v>
       </c>
       <c r="L191">
         <v>1495.39</v>
       </c>
       <c r="M191">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="N191" t="s">
         <v>30</v>
@@ -18582,22 +18602,22 @@
         <v>0.72</v>
       </c>
       <c r="W191">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X191">
         <v>0</v>
       </c>
       <c r="Y191">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="Z191">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="AA191">
         <v>1495.39</v>
       </c>
       <c r="AB191">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="AC191" t="s">
         <v>30</v>
@@ -18609,7 +18629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:31">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -18638,10 +18658,10 @@
         <v>0</v>
       </c>
       <c r="J192">
-        <v>23.21</v>
+        <v>0.15</v>
       </c>
       <c r="K192">
-        <v>31.74</v>
+        <v>0.36</v>
       </c>
       <c r="L192">
         <v>1485.99</v>
@@ -18683,10 +18703,10 @@
         <v>0</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z192">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="AA192">
         <v>1485.99</v>
@@ -18704,7 +18724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:31">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -18733,10 +18753,10 @@
         <v>0</v>
       </c>
       <c r="J193">
-        <v>31.8</v>
+        <v>0.52</v>
       </c>
       <c r="K193">
-        <v>20.72</v>
+        <v>0.04</v>
       </c>
       <c r="L193">
         <v>1511.78</v>
@@ -18799,7 +18819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:31">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -18828,10 +18848,10 @@
         <v>0</v>
       </c>
       <c r="J194">
-        <v>18.83</v>
+        <v>0.06</v>
       </c>
       <c r="K194">
-        <v>21.05</v>
+        <v>0.12</v>
       </c>
       <c r="L194">
         <v>108.7</v>
@@ -18876,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="Z194">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="AA194">
         <v>108.7</v>
@@ -18894,7 +18914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:31">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -18905,7 +18925,7 @@
         <v>1.57</v>
       </c>
       <c r="D195">
-        <v>87.51000000000001</v>
+        <v>87.51</v>
       </c>
       <c r="E195">
         <v>15.68</v>
@@ -18923,10 +18943,10 @@
         <v>0</v>
       </c>
       <c r="J195">
-        <v>18.56</v>
+        <v>0</v>
       </c>
       <c r="K195">
-        <v>28.92</v>
+        <v>0.3</v>
       </c>
       <c r="L195">
         <v>55.13</v>
@@ -18950,7 +18970,7 @@
         <v>1.57</v>
       </c>
       <c r="S195">
-        <v>87.51000000000001</v>
+        <v>87.51</v>
       </c>
       <c r="T195">
         <v>15.68</v>
@@ -18971,7 +18991,7 @@
         <v>0</v>
       </c>
       <c r="Z195">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="AA195">
         <v>55.13</v>
@@ -18989,7 +19009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:31">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -19018,10 +19038,10 @@
         <v>0</v>
       </c>
       <c r="J196">
-        <v>18.5</v>
+        <v>0.01</v>
       </c>
       <c r="K196">
-        <v>26.07</v>
+        <v>0.24</v>
       </c>
       <c r="L196">
         <v>102.7</v>
@@ -19066,7 +19086,7 @@
         <v>0</v>
       </c>
       <c r="Z196">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="AA196">
         <v>102.7</v>
@@ -19084,7 +19104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:31">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -19098,7 +19118,7 @@
         <v>47.36</v>
       </c>
       <c r="E197">
-        <v>36.62</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -19107,22 +19127,22 @@
         <v>0.43</v>
       </c>
       <c r="H197">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I197">
         <v>0</v>
       </c>
       <c r="J197">
-        <v>18.16</v>
+        <v>0.01</v>
       </c>
       <c r="K197">
-        <v>17.65</v>
+        <v>0</v>
       </c>
       <c r="L197">
         <v>133.82</v>
       </c>
       <c r="M197">
-        <v>1040.34</v>
+        <v>1040.3399999999999</v>
       </c>
       <c r="N197" t="s">
         <v>30</v>
@@ -19143,7 +19163,7 @@
         <v>47.36</v>
       </c>
       <c r="T197">
-        <v>36.62</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="U197">
         <v>0</v>
@@ -19152,7 +19172,7 @@
         <v>0.43</v>
       </c>
       <c r="W197">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="X197">
         <v>0</v>
@@ -19167,7 +19187,7 @@
         <v>133.82</v>
       </c>
       <c r="AB197">
-        <v>1040.34</v>
+        <v>1040.3399999999999</v>
       </c>
       <c r="AC197" t="s">
         <v>30</v>
@@ -19179,7 +19199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:31">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -19208,16 +19228,16 @@
         <v>0</v>
       </c>
       <c r="J198">
-        <v>21.05</v>
+        <v>0.06</v>
       </c>
       <c r="K198">
-        <v>27.2</v>
+        <v>0.22</v>
       </c>
       <c r="L198">
-        <v>284.47</v>
+        <v>284.47000000000003</v>
       </c>
       <c r="M198">
-        <v>539.92</v>
+        <v>539.91999999999996</v>
       </c>
       <c r="N198" t="s">
         <v>30</v>
@@ -19253,16 +19273,16 @@
         <v>0</v>
       </c>
       <c r="Y198">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z198">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="AA198">
-        <v>284.47</v>
+        <v>284.47000000000003</v>
       </c>
       <c r="AB198">
-        <v>539.92</v>
+        <v>539.91999999999996</v>
       </c>
       <c r="AC198" t="s">
         <v>30</v>
@@ -19274,7 +19294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:31">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -19288,7 +19308,7 @@
         <v>53.36</v>
       </c>
       <c r="E199">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -19303,13 +19323,13 @@
         <v>0</v>
       </c>
       <c r="J199">
-        <v>19.56</v>
+        <v>0.02</v>
       </c>
       <c r="K199">
-        <v>29.34</v>
+        <v>0.26</v>
       </c>
       <c r="L199">
-        <v>278.29</v>
+        <v>278.29000000000002</v>
       </c>
       <c r="M199">
         <v>904.54</v>
@@ -19333,7 +19353,7 @@
         <v>53.36</v>
       </c>
       <c r="T199">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="U199">
         <v>0</v>
@@ -19348,13 +19368,13 @@
         <v>0</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z199">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="AA199">
-        <v>278.29</v>
+        <v>278.29000000000002</v>
       </c>
       <c r="AB199">
         <v>904.54</v>
@@ -19369,7 +19389,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:31">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -19398,10 +19418,10 @@
         <v>0</v>
       </c>
       <c r="J200">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="K200">
-        <v>32.25</v>
+        <v>0.35</v>
       </c>
       <c r="L200">
         <v>415.77</v>
@@ -19443,10 +19463,10 @@
         <v>0</v>
       </c>
       <c r="Y200">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="Z200">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="AA200">
         <v>415.77</v>
@@ -19464,7 +19484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:31">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -19475,7 +19495,7 @@
         <v>2.74</v>
       </c>
       <c r="D201">
-        <v>89.45999999999999</v>
+        <v>89.46</v>
       </c>
       <c r="E201">
         <v>34.53</v>
@@ -19493,10 +19513,10 @@
         <v>0</v>
       </c>
       <c r="J201">
-        <v>18.82</v>
+        <v>0</v>
       </c>
       <c r="K201">
-        <v>19.52</v>
+        <v>0.03</v>
       </c>
       <c r="L201">
         <v>409.81</v>
@@ -19520,7 +19540,7 @@
         <v>2.74</v>
       </c>
       <c r="S201">
-        <v>89.45999999999999</v>
+        <v>89.46</v>
       </c>
       <c r="T201">
         <v>34.53</v>
@@ -19541,7 +19561,7 @@
         <v>0</v>
       </c>
       <c r="Z201">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA201">
         <v>409.81</v>
@@ -19559,7 +19579,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:31">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -19588,16 +19608,16 @@
         <v>0</v>
       </c>
       <c r="J202">
-        <v>19.94</v>
+        <v>0.03</v>
       </c>
       <c r="K202">
-        <v>19.42</v>
+        <v>0.02</v>
       </c>
       <c r="L202">
         <v>598.16</v>
       </c>
       <c r="M202">
-        <v>935.0599999999999</v>
+        <v>935.06</v>
       </c>
       <c r="N202" t="s">
         <v>30</v>
@@ -19633,16 +19653,16 @@
         <v>0</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z202">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="AA202">
         <v>598.16</v>
       </c>
       <c r="AB202">
-        <v>935.0599999999999</v>
+        <v>935.06</v>
       </c>
       <c r="AC202" t="s">
         <v>30</v>
@@ -19654,7 +19674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="203" spans="1:31">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -19665,7 +19685,7 @@
         <v>4.37</v>
       </c>
       <c r="D203">
-        <v>78.15000000000001</v>
+        <v>78.150000000000006</v>
       </c>
       <c r="E203">
         <v>52.28</v>
@@ -19683,10 +19703,10 @@
         <v>0</v>
       </c>
       <c r="J203">
-        <v>24.77</v>
+        <v>0.27</v>
       </c>
       <c r="K203">
-        <v>33.7</v>
+        <v>0.38</v>
       </c>
       <c r="L203">
         <v>785.74</v>
@@ -19710,7 +19730,7 @@
         <v>4.37</v>
       </c>
       <c r="S203">
-        <v>78.15000000000001</v>
+        <v>78.150000000000006</v>
       </c>
       <c r="T203">
         <v>52.28</v>
@@ -19728,10 +19748,10 @@
         <v>0</v>
       </c>
       <c r="Y203">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="Z203">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="AA203">
         <v>785.74</v>
@@ -19749,7 +19769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:31">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -19778,10 +19798,10 @@
         <v>0</v>
       </c>
       <c r="J204">
-        <v>22.96</v>
+        <v>0.08</v>
       </c>
       <c r="K204">
-        <v>34.68</v>
+        <v>0.39</v>
       </c>
       <c r="L204">
         <v>1066.49</v>
@@ -19826,7 +19846,7 @@
         <v>0</v>
       </c>
       <c r="Z204">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="AA204">
         <v>1066.49</v>
@@ -19844,7 +19864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:31">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -19858,7 +19878,7 @@
         <v>48.69</v>
       </c>
       <c r="E205">
-        <v>37.77</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -19873,10 +19893,10 @@
         <v>0</v>
       </c>
       <c r="J205">
-        <v>21.43</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K205">
-        <v>25</v>
+        <v>0.1</v>
       </c>
       <c r="L205">
         <v>1344.95</v>
@@ -19903,7 +19923,7 @@
         <v>48.69</v>
       </c>
       <c r="T205">
-        <v>37.77</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="U205">
         <v>0</v>
@@ -19918,10 +19938,10 @@
         <v>0</v>
       </c>
       <c r="Y205">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z205">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="AA205">
         <v>1344.95</v>
@@ -19939,7 +19959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="206" spans="1:31">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -19950,7 +19970,7 @@
         <v>3.08</v>
       </c>
       <c r="D206">
-        <v>76.70999999999999</v>
+        <v>76.709999999999994</v>
       </c>
       <c r="E206">
         <v>24.26</v>
@@ -19959,7 +19979,7 @@
         <v>0</v>
       </c>
       <c r="G206">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H206">
         <v>0.71</v>
@@ -19968,10 +19988,10 @@
         <v>0</v>
       </c>
       <c r="J206">
-        <v>20.93</v>
+        <v>0.08</v>
       </c>
       <c r="K206">
-        <v>21.28</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L206">
         <v>1322.29</v>
@@ -19995,7 +20015,7 @@
         <v>3.08</v>
       </c>
       <c r="S206">
-        <v>76.70999999999999</v>
+        <v>76.709999999999994</v>
       </c>
       <c r="T206">
         <v>24.26</v>
@@ -20004,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="V206">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W206">
         <v>0.71</v>
@@ -20013,10 +20033,10 @@
         <v>0</v>
       </c>
       <c r="Y206">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z206">
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA206">
         <v>1322.29</v>
@@ -20034,7 +20054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:31">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -20057,16 +20077,16 @@
         <v>0.19</v>
       </c>
       <c r="H207">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I207">
         <v>0</v>
       </c>
       <c r="J207">
-        <v>20.58</v>
+        <v>0.01</v>
       </c>
       <c r="K207">
-        <v>26.66</v>
+        <v>0.17</v>
       </c>
       <c r="L207">
         <v>1133.82</v>
@@ -20102,16 +20122,16 @@
         <v>0.19</v>
       </c>
       <c r="W207">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X207">
         <v>0</v>
       </c>
       <c r="Y207">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Z207">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="AA207">
         <v>1133.82</v>
@@ -20129,7 +20149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:31">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -20152,16 +20172,16 @@
         <v>0.19</v>
       </c>
       <c r="H208">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I208">
         <v>0</v>
       </c>
       <c r="J208">
-        <v>21.05</v>
+        <v>0.08</v>
       </c>
       <c r="K208">
-        <v>26.42</v>
+        <v>0.26</v>
       </c>
       <c r="L208">
         <v>1230.56</v>
@@ -20197,7 +20217,7 @@
         <v>0.19</v>
       </c>
       <c r="W208">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X208">
         <v>0</v>
@@ -20206,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="Z208">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="AA208">
         <v>1230.56</v>
@@ -20224,7 +20244,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:31">
+    <row r="209" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -20253,10 +20273,10 @@
         <v>0</v>
       </c>
       <c r="J209">
-        <v>20.54</v>
+        <v>0.01</v>
       </c>
       <c r="K209">
-        <v>39.27</v>
+        <v>0.4</v>
       </c>
       <c r="L209">
         <v>1440.2</v>
@@ -20301,7 +20321,7 @@
         <v>0</v>
       </c>
       <c r="Z209">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="AA209">
         <v>1440.2</v>
@@ -20319,7 +20339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="210" spans="1:31">
+    <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -20351,7 +20371,7 @@
         <v>0</v>
       </c>
       <c r="K210">
-        <v>40.99</v>
+        <v>0.41</v>
       </c>
       <c r="L210">
         <v>1534.17</v>
@@ -20396,7 +20416,7 @@
         <v>0</v>
       </c>
       <c r="Z210">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="AA210">
         <v>1534.17</v>
@@ -20414,7 +20434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:31">
+    <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -20428,7 +20448,7 @@
         <v>25.59</v>
       </c>
       <c r="E211">
-        <v>35.37</v>
+        <v>35.369999999999997</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -20443,16 +20463,16 @@
         <v>0</v>
       </c>
       <c r="J211">
-        <v>17.26</v>
+        <v>0</v>
       </c>
       <c r="K211">
-        <v>23.58</v>
+        <v>0.13</v>
       </c>
       <c r="L211">
         <v>121.78</v>
       </c>
       <c r="M211">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="N211" t="s">
         <v>30</v>
@@ -20473,7 +20493,7 @@
         <v>25.59</v>
       </c>
       <c r="T211">
-        <v>35.37</v>
+        <v>35.369999999999997</v>
       </c>
       <c r="U211">
         <v>0</v>
@@ -20491,13 +20511,13 @@
         <v>0</v>
       </c>
       <c r="Z211">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="AA211">
         <v>121.78</v>
       </c>
       <c r="AB211">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="AC211" t="s">
         <v>30</v>
@@ -20509,7 +20529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:31">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -20538,13 +20558,13 @@
         <v>0</v>
       </c>
       <c r="J212">
-        <v>21.11</v>
+        <v>0.1</v>
       </c>
       <c r="K212">
-        <v>52.97</v>
+        <v>0.46</v>
       </c>
       <c r="L212">
-        <v>134.98</v>
+        <v>134.97999999999999</v>
       </c>
       <c r="M212">
         <v>192.82</v>
@@ -20583,13 +20603,13 @@
         <v>0</v>
       </c>
       <c r="Y212">
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Z212">
-        <v>0.2</v>
+        <v>0.49</v>
       </c>
       <c r="AA212">
-        <v>134.98</v>
+        <v>134.97999999999999</v>
       </c>
       <c r="AB212">
         <v>192.82</v>
@@ -20604,7 +20624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:31">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -20633,10 +20653,10 @@
         <v>0</v>
       </c>
       <c r="J213">
-        <v>36.67</v>
+        <v>0.48</v>
       </c>
       <c r="K213">
-        <v>46.02</v>
+        <v>0.52</v>
       </c>
       <c r="L213">
         <v>121.94</v>
@@ -20678,10 +20698,10 @@
         <v>0</v>
       </c>
       <c r="Y213">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="Z213">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="AA213">
         <v>121.94</v>
@@ -20699,7 +20719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:31">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -20710,7 +20730,7 @@
         <v>1.24</v>
       </c>
       <c r="D214">
-        <v>74.70999999999999</v>
+        <v>74.709999999999994</v>
       </c>
       <c r="E214">
         <v>94.61</v>
@@ -20728,10 +20748,10 @@
         <v>0</v>
       </c>
       <c r="J214">
-        <v>33.98</v>
+        <v>0.47</v>
       </c>
       <c r="K214">
-        <v>30.87</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L214">
         <v>345.25</v>
@@ -20755,7 +20775,7 @@
         <v>1.24</v>
       </c>
       <c r="S214">
-        <v>74.70999999999999</v>
+        <v>74.709999999999994</v>
       </c>
       <c r="T214">
         <v>94.61</v>
@@ -20773,10 +20793,10 @@
         <v>0</v>
       </c>
       <c r="Y214">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z214">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="AA214">
         <v>345.25</v>
@@ -20794,7 +20814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:31">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -20814,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="G215">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H215">
         <v>0.93</v>
@@ -20823,10 +20843,10 @@
         <v>0</v>
       </c>
       <c r="J215">
-        <v>33.62</v>
+        <v>0.84</v>
       </c>
       <c r="K215">
-        <v>45.25</v>
+        <v>0.53</v>
       </c>
       <c r="L215">
         <v>50.12</v>
@@ -20859,7 +20879,7 @@
         <v>0</v>
       </c>
       <c r="V215">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="W215">
         <v>0.93</v>
@@ -20868,10 +20888,10 @@
         <v>0</v>
       </c>
       <c r="Y215">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="Z215">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="AA215">
         <v>50.12</v>
@@ -20889,7 +20909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:31">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -20918,10 +20938,10 @@
         <v>0</v>
       </c>
       <c r="J216">
-        <v>23.71</v>
+        <v>0.25</v>
       </c>
       <c r="K216">
-        <v>29.48</v>
+        <v>0.25</v>
       </c>
       <c r="L216">
         <v>282.99</v>
@@ -20984,7 +21004,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:31">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -20998,7 +21018,7 @@
         <v>70.7</v>
       </c>
       <c r="E217">
-        <v>81.09999999999999</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -21013,10 +21033,10 @@
         <v>0</v>
       </c>
       <c r="J217">
-        <v>25.78</v>
+        <v>0.16</v>
       </c>
       <c r="K217">
-        <v>40.98</v>
+        <v>0.35</v>
       </c>
       <c r="L217">
         <v>551.4</v>
@@ -21043,7 +21063,7 @@
         <v>70.7</v>
       </c>
       <c r="T217">
-        <v>81.09999999999999</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="U217">
         <v>0</v>
@@ -21058,10 +21078,10 @@
         <v>0</v>
       </c>
       <c r="Y217">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="Z217">
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="AA217">
         <v>551.4</v>
@@ -21079,7 +21099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:31">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -21090,7 +21110,7 @@
         <v>2.48</v>
       </c>
       <c r="D218">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E218">
         <v>100.41</v>
@@ -21108,10 +21128,10 @@
         <v>0</v>
       </c>
       <c r="J218">
-        <v>22.52</v>
+        <v>0.12</v>
       </c>
       <c r="K218">
-        <v>39.23</v>
+        <v>0.36</v>
       </c>
       <c r="L218">
         <v>578.77</v>
@@ -21135,7 +21155,7 @@
         <v>2.48</v>
       </c>
       <c r="S218">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="T218">
         <v>100.41</v>
@@ -21153,10 +21173,10 @@
         <v>0</v>
       </c>
       <c r="Y218">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z218">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="AA218">
         <v>578.77</v>
@@ -21174,7 +21194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:31">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -21203,10 +21223,10 @@
         <v>0</v>
       </c>
       <c r="J219">
-        <v>29.76</v>
+        <v>0.62</v>
       </c>
       <c r="K219">
-        <v>22.64</v>
+        <v>0.2</v>
       </c>
       <c r="L219">
         <v>601.48</v>
@@ -21269,7 +21289,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:31">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -21298,10 +21318,10 @@
         <v>0</v>
       </c>
       <c r="J220">
-        <v>24.43</v>
+        <v>0.18</v>
       </c>
       <c r="K220">
-        <v>32.32</v>
+        <v>0.38</v>
       </c>
       <c r="L220">
         <v>732.1</v>
@@ -21343,10 +21363,10 @@
         <v>0</v>
       </c>
       <c r="Y220">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Z220">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="AA220">
         <v>732.1</v>
@@ -21364,7 +21384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:31">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -21393,10 +21413,10 @@
         <v>0</v>
       </c>
       <c r="J221">
-        <v>32.81</v>
+        <v>0.25</v>
       </c>
       <c r="K221">
-        <v>31.73</v>
+        <v>0.25</v>
       </c>
       <c r="L221">
         <v>798.62</v>
@@ -21438,10 +21458,10 @@
         <v>0</v>
       </c>
       <c r="Y221">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="Z221">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="AA221">
         <v>798.62</v>
@@ -21459,7 +21479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:31">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -21467,10 +21487,10 @@
         <v>166350</v>
       </c>
       <c r="C222">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="D222">
-        <v>71.98999999999999</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="E222">
         <v>63.32</v>
@@ -21482,16 +21502,16 @@
         <v>0.42</v>
       </c>
       <c r="H222">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I222">
         <v>0</v>
       </c>
       <c r="J222">
-        <v>24.79</v>
+        <v>0.1</v>
       </c>
       <c r="K222">
-        <v>39.21</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L222">
         <v>914.34</v>
@@ -21512,10 +21532,10 @@
         <v>166350</v>
       </c>
       <c r="R222">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="S222">
-        <v>71.98999999999999</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="T222">
         <v>63.32</v>
@@ -21527,16 +21547,16 @@
         <v>0.42</v>
       </c>
       <c r="W222">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X222">
         <v>0</v>
       </c>
       <c r="Y222">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="Z222">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="AA222">
         <v>914.34</v>
@@ -21554,7 +21574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:31">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -21583,13 +21603,13 @@
         <v>0</v>
       </c>
       <c r="J223">
-        <v>26.65</v>
+        <v>0.25</v>
       </c>
       <c r="K223">
-        <v>37.03</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L223">
-        <v>989.1900000000001</v>
+        <v>989.19</v>
       </c>
       <c r="M223">
         <v>1000.7</v>
@@ -21628,13 +21648,13 @@
         <v>0</v>
       </c>
       <c r="Y223">
-        <v>0.33</v>
+        <v>0.78</v>
       </c>
       <c r="Z223">
-        <v>0.15</v>
+        <v>0.38</v>
       </c>
       <c r="AA223">
-        <v>989.1900000000001</v>
+        <v>989.19</v>
       </c>
       <c r="AB223">
         <v>1000.7</v>
@@ -21649,7 +21669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:31">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -21660,7 +21680,7 @@
         <v>2.33</v>
       </c>
       <c r="D224">
-        <v>71.59999999999999</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="E224">
         <v>46.29</v>
@@ -21678,10 +21698,10 @@
         <v>0</v>
       </c>
       <c r="J224">
-        <v>21.82</v>
+        <v>0.06</v>
       </c>
       <c r="K224">
-        <v>48.71</v>
+        <v>0.39</v>
       </c>
       <c r="L224">
         <v>1180.33</v>
@@ -21705,7 +21725,7 @@
         <v>2.33</v>
       </c>
       <c r="S224">
-        <v>71.59999999999999</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="T224">
         <v>46.29</v>
@@ -21723,10 +21743,10 @@
         <v>0</v>
       </c>
       <c r="Y224">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="Z224">
-        <v>0.21</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AA224">
         <v>1180.33</v>
@@ -21744,7 +21764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:31">
+    <row r="225" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -21773,13 +21793,13 @@
         <v>0</v>
       </c>
       <c r="J225">
-        <v>23.56</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K225">
-        <v>34.26</v>
+        <v>0.4</v>
       </c>
       <c r="L225">
-        <v>1129.89</v>
+        <v>1129.8900000000001</v>
       </c>
       <c r="M225">
         <v>205.69</v>
@@ -21818,13 +21838,13 @@
         <v>0</v>
       </c>
       <c r="Y225">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="Z225">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="AA225">
-        <v>1129.89</v>
+        <v>1129.8900000000001</v>
       </c>
       <c r="AB225">
         <v>205.69</v>
@@ -21839,7 +21859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:31">
+    <row r="226" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -21853,7 +21873,7 @@
         <v>45.32</v>
       </c>
       <c r="E226">
-        <v>38.66</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -21868,10 +21888,10 @@
         <v>0</v>
       </c>
       <c r="J226">
-        <v>26.41</v>
+        <v>0.08</v>
       </c>
       <c r="K226">
-        <v>35.99</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L226">
         <v>1319.11</v>
@@ -21898,7 +21918,7 @@
         <v>45.32</v>
       </c>
       <c r="T226">
-        <v>38.66</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="U226">
         <v>0</v>
@@ -21913,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="Y226">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="Z226">
-        <v>0.15</v>
+        <v>0.38</v>
       </c>
       <c r="AA226">
         <v>1319.11</v>
@@ -21934,7 +21954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:31">
+    <row r="227" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -21945,7 +21965,7 @@
         <v>2.83</v>
       </c>
       <c r="D227">
-        <v>99.06999999999999</v>
+        <v>99.07</v>
       </c>
       <c r="E227">
         <v>73.7</v>
@@ -21963,13 +21983,13 @@
         <v>0</v>
       </c>
       <c r="J227">
-        <v>39.1</v>
+        <v>0.61</v>
       </c>
       <c r="K227">
-        <v>86.33</v>
+        <v>0.8</v>
       </c>
       <c r="L227">
-        <v>1276.15</v>
+        <v>1276.1500000000001</v>
       </c>
       <c r="M227">
         <v>148.6</v>
@@ -21990,7 +22010,7 @@
         <v>2.83</v>
       </c>
       <c r="S227">
-        <v>99.06999999999999</v>
+        <v>99.07</v>
       </c>
       <c r="T227">
         <v>73.7</v>
@@ -22008,13 +22028,13 @@
         <v>0</v>
       </c>
       <c r="Y227">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="Z227">
-        <v>0.3</v>
+        <v>0.78</v>
       </c>
       <c r="AA227">
-        <v>1276.15</v>
+        <v>1276.1500000000001</v>
       </c>
       <c r="AB227">
         <v>148.6</v>
@@ -22029,7 +22049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:31">
+    <row r="228" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -22037,7 +22057,7 @@
         <v>29901</v>
       </c>
       <c r="C228">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D228">
         <v>72.75</v>
@@ -22049,7 +22069,7 @@
         <v>0</v>
       </c>
       <c r="G228">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H228">
         <v>0.72</v>
@@ -22058,16 +22078,16 @@
         <v>0</v>
       </c>
       <c r="J228">
-        <v>64.48999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="K228">
-        <v>66.73</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="L228">
         <v>1418.01</v>
       </c>
       <c r="M228">
-        <v>93.54000000000001</v>
+        <v>93.54</v>
       </c>
       <c r="N228" t="s">
         <v>30</v>
@@ -22082,7 +22102,7 @@
         <v>29901</v>
       </c>
       <c r="R228">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="S228">
         <v>72.75</v>
@@ -22094,7 +22114,7 @@
         <v>0</v>
       </c>
       <c r="V228">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W228">
         <v>0.72</v>
@@ -22103,16 +22123,16 @@
         <v>0</v>
       </c>
       <c r="Y228">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="Z228">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="AA228">
         <v>1418.01</v>
       </c>
       <c r="AB228">
-        <v>93.54000000000001</v>
+        <v>93.54</v>
       </c>
       <c r="AC228" t="s">
         <v>30</v>
@@ -22124,7 +22144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:31">
+    <row r="229" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -22153,10 +22173,10 @@
         <v>0</v>
       </c>
       <c r="J229">
-        <v>38.97</v>
+        <v>0.37</v>
       </c>
       <c r="K229">
-        <v>49.87</v>
+        <v>0.5</v>
       </c>
       <c r="L229">
         <v>1482.43</v>
@@ -22198,10 +22218,10 @@
         <v>0</v>
       </c>
       <c r="Y229">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="Z229">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="AA229">
         <v>1482.43</v>
@@ -22219,7 +22239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:31">
+    <row r="230" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -22248,10 +22268,10 @@
         <v>0</v>
       </c>
       <c r="J230">
-        <v>29.34</v>
+        <v>0.32</v>
       </c>
       <c r="K230">
-        <v>35.2</v>
+        <v>0.3</v>
       </c>
       <c r="L230">
         <v>1497.48</v>
@@ -22293,10 +22313,10 @@
         <v>0</v>
       </c>
       <c r="Y230">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="Z230">
-        <v>0.12</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA230">
         <v>1497.48</v>
@@ -22314,7 +22334,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:31">
+    <row r="231" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -22343,16 +22363,16 @@
         <v>0</v>
       </c>
       <c r="J231">
-        <v>103.5</v>
+        <v>1</v>
       </c>
       <c r="K231">
-        <v>121.86</v>
+        <v>0.94</v>
       </c>
       <c r="L231">
         <v>1536.99</v>
       </c>
       <c r="M231">
-        <v>568.1900000000001</v>
+        <v>568.19000000000005</v>
       </c>
       <c r="N231" t="s">
         <v>30</v>
@@ -22388,16 +22408,16 @@
         <v>0</v>
       </c>
       <c r="Y231">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="Z231">
-        <v>0.36</v>
+        <v>0.94</v>
       </c>
       <c r="AA231">
         <v>1536.99</v>
       </c>
       <c r="AB231">
-        <v>568.1900000000001</v>
+        <v>568.19000000000005</v>
       </c>
       <c r="AC231" t="s">
         <v>30</v>
